--- a/research/traditional_assets/database/data/ireland/ireland_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_healthcare_support_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08807574435978699</v>
+        <v>0.08800502467933727</v>
       </c>
       <c r="C2">
-        <v>1071.171872802671</v>
+        <v>1062.32133074348</v>
       </c>
       <c r="D2">
-        <v>968.2718728026705</v>
+        <v>969.8943307434803</v>
       </c>
       <c r="E2">
-        <v>-448.1</v>
+        <v>-437.627</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.473</v>
       </c>
       <c r="G2">
         <v>102.9</v>
@@ -1457,28 +1457,28 @@
         <v>109.325</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5267919000000001</v>
       </c>
       <c r="N2">
-        <v>109.325</v>
+        <v>108.7982081</v>
       </c>
       <c r="O2">
-        <v>13.665625</v>
+        <v>13.5997760125</v>
       </c>
       <c r="P2">
-        <v>95.65937499999998</v>
+        <v>95.19843208749998</v>
       </c>
       <c r="Q2">
-        <v>109.959375</v>
+        <v>109.4984320875</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08807574435978699</v>
+        <v>0.08844939361549219</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738457</v>
+        <v>0.8313160648405338</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>207.5297664979283</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08800502467933727</v>
+        <v>0.08793430499888752</v>
       </c>
       <c r="C3">
-        <v>1062.32133074348</v>
+        <v>1053.476235063773</v>
       </c>
       <c r="D3">
-        <v>969.8943307434803</v>
+        <v>971.5222350637725</v>
       </c>
       <c r="E3">
-        <v>-437.627</v>
+        <v>-427.154</v>
       </c>
       <c r="F3">
-        <v>10.473</v>
+        <v>20.94600000000001</v>
       </c>
       <c r="G3">
         <v>102.9</v>
@@ -1539,28 +1539,28 @@
         <v>109.325</v>
       </c>
       <c r="M3">
-        <v>0.5267919000000001</v>
+        <v>1.0535838</v>
       </c>
       <c r="N3">
-        <v>108.7982081</v>
+        <v>108.2714162</v>
       </c>
       <c r="O3">
-        <v>13.5997760125</v>
+        <v>13.533927025</v>
       </c>
       <c r="P3">
-        <v>95.19843208749998</v>
+        <v>94.73748917499999</v>
       </c>
       <c r="Q3">
-        <v>109.4984320875</v>
+        <v>109.037489175</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08844939361549219</v>
+        <v>0.08883066836621176</v>
       </c>
       <c r="T3">
-        <v>0.8313160648405338</v>
+        <v>0.8387478193983786</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>207.5297664979283</v>
+        <v>103.7648832489641</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08793430499888752</v>
+        <v>0.0878635853184378</v>
       </c>
       <c r="C4">
-        <v>1053.476235063773</v>
+        <v>1044.63661323383</v>
       </c>
       <c r="D4">
-        <v>971.5222350637725</v>
+        <v>973.1556132338304</v>
       </c>
       <c r="E4">
-        <v>-427.154</v>
+        <v>-416.681</v>
       </c>
       <c r="F4">
-        <v>20.94600000000001</v>
+        <v>31.419</v>
       </c>
       <c r="G4">
         <v>102.9</v>
@@ -1621,28 +1621,28 @@
         <v>109.325</v>
       </c>
       <c r="M4">
-        <v>1.0535838</v>
+        <v>1.5803757</v>
       </c>
       <c r="N4">
-        <v>108.2714162</v>
+        <v>107.7446243</v>
       </c>
       <c r="O4">
-        <v>13.533927025</v>
+        <v>13.4680780375</v>
       </c>
       <c r="P4">
-        <v>94.73748917499999</v>
+        <v>94.27654626249999</v>
       </c>
       <c r="Q4">
-        <v>109.037489175</v>
+        <v>108.5765462625</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08883066836621176</v>
+        <v>0.08921980445199773</v>
       </c>
       <c r="T4">
-        <v>0.8387478193983786</v>
+        <v>0.8463328060089627</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.7648832489641</v>
+        <v>69.17658883264276</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0878635853184378</v>
+        <v>0.08779286563798805</v>
       </c>
       <c r="C5">
-        <v>1044.63661323383</v>
+        <v>1035.802492908989</v>
       </c>
       <c r="D5">
-        <v>973.1556132338304</v>
+        <v>974.7944929089892</v>
       </c>
       <c r="E5">
-        <v>-416.681</v>
+        <v>-406.208</v>
       </c>
       <c r="F5">
-        <v>31.419</v>
+        <v>41.89200000000001</v>
       </c>
       <c r="G5">
         <v>102.9</v>
@@ -1703,28 +1703,28 @@
         <v>109.325</v>
       </c>
       <c r="M5">
-        <v>1.5803757</v>
+        <v>2.1071676</v>
       </c>
       <c r="N5">
-        <v>107.7446243</v>
+        <v>107.2178324</v>
       </c>
       <c r="O5">
-        <v>13.4680780375</v>
+        <v>13.40222905</v>
       </c>
       <c r="P5">
-        <v>94.27654626249999</v>
+        <v>93.81560334999999</v>
       </c>
       <c r="Q5">
-        <v>108.5765462625</v>
+        <v>108.11560335</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08921980445199773</v>
+        <v>0.08961704753957089</v>
       </c>
       <c r="T5">
-        <v>0.8463328060089627</v>
+        <v>0.8540758131739338</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.17658883264276</v>
+        <v>51.88244162448206</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08779286563798805</v>
+        <v>0.08772214595753833</v>
       </c>
       <c r="C6">
-        <v>1035.802492908989</v>
+        <v>1026.973901931192</v>
       </c>
       <c r="D6">
-        <v>974.7944929089892</v>
+        <v>976.4389019311919</v>
       </c>
       <c r="E6">
-        <v>-406.208</v>
+        <v>-395.735</v>
       </c>
       <c r="F6">
-        <v>41.89200000000001</v>
+        <v>52.36500000000001</v>
       </c>
       <c r="G6">
         <v>102.9</v>
@@ -1785,28 +1785,28 @@
         <v>109.325</v>
       </c>
       <c r="M6">
-        <v>2.1071676</v>
+        <v>2.6339595</v>
       </c>
       <c r="N6">
-        <v>107.2178324</v>
+        <v>106.6910405</v>
       </c>
       <c r="O6">
-        <v>13.40222905</v>
+        <v>13.3363800625</v>
       </c>
       <c r="P6">
-        <v>93.81560334999999</v>
+        <v>93.35466043749999</v>
       </c>
       <c r="Q6">
-        <v>108.11560335</v>
+        <v>107.6546604375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08961704753957089</v>
+        <v>0.09002265363951403</v>
       </c>
       <c r="T6">
-        <v>0.8540758131739338</v>
+        <v>0.8619818310160623</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.88244162448206</v>
+        <v>41.50595329958565</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08772214595753833</v>
+        <v>0.08765142627708858</v>
       </c>
       <c r="C7">
-        <v>1026.973901931192</v>
+        <v>1018.150868330571</v>
       </c>
       <c r="D7">
-        <v>976.4389019311919</v>
+        <v>978.0888683305709</v>
       </c>
       <c r="E7">
-        <v>-395.735</v>
+        <v>-385.262</v>
       </c>
       <c r="F7">
-        <v>52.36500000000001</v>
+        <v>62.83800000000002</v>
       </c>
       <c r="G7">
         <v>102.9</v>
@@ -1867,28 +1867,28 @@
         <v>109.325</v>
       </c>
       <c r="M7">
-        <v>2.6339595</v>
+        <v>3.160751400000001</v>
       </c>
       <c r="N7">
-        <v>106.6910405</v>
+        <v>106.1642486</v>
       </c>
       <c r="O7">
-        <v>13.3363800625</v>
+        <v>13.270531075</v>
       </c>
       <c r="P7">
-        <v>93.35466043749999</v>
+        <v>92.893717525</v>
       </c>
       <c r="Q7">
-        <v>107.6546604375</v>
+        <v>107.193717525</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09002265363951403</v>
+        <v>0.09043688965647723</v>
       </c>
       <c r="T7">
-        <v>0.8619818310160623</v>
+        <v>0.8700560620037681</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.50595329958565</v>
+        <v>34.58829441632138</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08765142627708858</v>
+        <v>0.08758070659663886</v>
       </c>
       <c r="C8">
-        <v>1018.150868330571</v>
+        <v>1009.333420327036</v>
       </c>
       <c r="D8">
-        <v>978.0888683305709</v>
+        <v>979.7444203270356</v>
       </c>
       <c r="E8">
-        <v>-385.262</v>
+        <v>-374.789</v>
       </c>
       <c r="F8">
-        <v>62.83800000000001</v>
+        <v>73.31100000000001</v>
       </c>
       <c r="G8">
         <v>102.9</v>
@@ -1949,28 +1949,28 @@
         <v>109.325</v>
       </c>
       <c r="M8">
-        <v>3.1607514</v>
+        <v>3.6875433</v>
       </c>
       <c r="N8">
-        <v>106.1642486</v>
+        <v>105.6374567</v>
       </c>
       <c r="O8">
-        <v>13.270531075</v>
+        <v>13.2046820875</v>
       </c>
       <c r="P8">
-        <v>92.893717525</v>
+        <v>92.43277461249998</v>
       </c>
       <c r="Q8">
-        <v>107.193717525</v>
+        <v>106.7327746125</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09043688965647723</v>
+        <v>0.09086003397488049</v>
       </c>
       <c r="T8">
-        <v>0.8700560620037681</v>
+        <v>0.8783039323675533</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.58829441632138</v>
+        <v>29.64710949970404</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08758070659663884</v>
+        <v>0.08750998691618914</v>
       </c>
       <c r="C9">
-        <v>1009.333420327036</v>
+        <v>1000.521586331886</v>
       </c>
       <c r="D9">
-        <v>979.7444203270358</v>
+        <v>981.4055863318857</v>
       </c>
       <c r="E9">
-        <v>-374.789</v>
+        <v>-364.316</v>
       </c>
       <c r="F9">
-        <v>73.31100000000002</v>
+        <v>83.78400000000002</v>
       </c>
       <c r="G9">
         <v>102.9</v>
@@ -2031,28 +2031,28 @@
         <v>109.325</v>
       </c>
       <c r="M9">
-        <v>3.687543300000001</v>
+        <v>4.214335200000001</v>
       </c>
       <c r="N9">
-        <v>105.6374567</v>
+        <v>105.1106648</v>
       </c>
       <c r="O9">
-        <v>13.2046820875</v>
+        <v>13.1388331</v>
       </c>
       <c r="P9">
-        <v>92.43277461249998</v>
+        <v>91.9718317</v>
       </c>
       <c r="Q9">
-        <v>106.7327746125</v>
+        <v>106.2718317</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09086003397488049</v>
+        <v>0.09129237708281428</v>
       </c>
       <c r="T9">
-        <v>0.8783039323675533</v>
+        <v>0.8867311042609863</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.64710949970403</v>
+        <v>25.94122081224103</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08750998691618914</v>
+        <v>0.08743926723573939</v>
       </c>
       <c r="C10">
-        <v>1000.521586331886</v>
+        <v>991.7153949494354</v>
       </c>
       <c r="D10">
-        <v>981.4055863318857</v>
+        <v>983.0723949494355</v>
       </c>
       <c r="E10">
-        <v>-364.316</v>
+        <v>-353.843</v>
       </c>
       <c r="F10">
-        <v>83.78400000000002</v>
+        <v>94.25700000000002</v>
       </c>
       <c r="G10">
         <v>102.9</v>
@@ -2113,28 +2113,28 @@
         <v>109.325</v>
       </c>
       <c r="M10">
-        <v>4.214335200000001</v>
+        <v>4.741127100000001</v>
       </c>
       <c r="N10">
-        <v>105.1106648</v>
+        <v>104.5838729</v>
       </c>
       <c r="O10">
-        <v>13.1388331</v>
+        <v>13.0729841125</v>
       </c>
       <c r="P10">
-        <v>91.9718317</v>
+        <v>91.51088878749999</v>
       </c>
       <c r="Q10">
-        <v>106.2718317</v>
+        <v>105.8108887875</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09129237708281428</v>
+        <v>0.09173422223707625</v>
       </c>
       <c r="T10">
-        <v>0.8867311042609863</v>
+        <v>0.8953434887235054</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.94122081224103</v>
+        <v>23.05886294421425</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08743926723573939</v>
+        <v>0.08736854755528967</v>
       </c>
       <c r="C11">
-        <v>991.7153949494354</v>
+        <v>982.9148749786523</v>
       </c>
       <c r="D11">
-        <v>983.0723949494355</v>
+        <v>984.7448749786523</v>
       </c>
       <c r="E11">
-        <v>-353.843</v>
+        <v>-343.37</v>
       </c>
       <c r="F11">
-        <v>94.25700000000002</v>
+        <v>104.73</v>
       </c>
       <c r="G11">
         <v>102.9</v>
@@ -2195,28 +2195,28 @@
         <v>109.325</v>
       </c>
       <c r="M11">
-        <v>4.741127100000001</v>
+        <v>5.267919</v>
       </c>
       <c r="N11">
-        <v>104.5838729</v>
+        <v>104.057081</v>
       </c>
       <c r="O11">
-        <v>13.0729841125</v>
+        <v>13.007135125</v>
       </c>
       <c r="P11">
-        <v>91.51088878749999</v>
+        <v>91.04994587499999</v>
       </c>
       <c r="Q11">
-        <v>105.8108887875</v>
+        <v>105.349945875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09173422223707625</v>
+        <v>0.09218588617254407</v>
       </c>
       <c r="T11">
-        <v>0.8953434887235054</v>
+        <v>0.9041472595074141</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.05886294421425</v>
+        <v>20.75297664979283</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08736854755528967</v>
+        <v>0.08729782787483993</v>
       </c>
       <c r="C12">
-        <v>982.9148749786523</v>
+        <v>974.1200554148197</v>
       </c>
       <c r="D12">
-        <v>984.7448749786523</v>
+        <v>986.4230554148197</v>
       </c>
       <c r="E12">
-        <v>-343.37</v>
+        <v>-332.897</v>
       </c>
       <c r="F12">
-        <v>104.73</v>
+        <v>115.203</v>
       </c>
       <c r="G12">
         <v>102.9</v>
@@ -2277,28 +2277,28 @@
         <v>109.325</v>
       </c>
       <c r="M12">
-        <v>5.267919000000001</v>
+        <v>5.794710900000001</v>
       </c>
       <c r="N12">
-        <v>104.057081</v>
+        <v>103.5302891</v>
       </c>
       <c r="O12">
-        <v>13.007135125</v>
+        <v>12.9412861375</v>
       </c>
       <c r="P12">
-        <v>91.04994587499999</v>
+        <v>90.58900296249999</v>
       </c>
       <c r="Q12">
-        <v>105.349945875</v>
+        <v>104.8890029625</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09218588617254407</v>
+        <v>0.09264769985937071</v>
       </c>
       <c r="T12">
-        <v>0.9041472595074141</v>
+        <v>0.9131488678370285</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.75297664979282</v>
+        <v>18.86634240890257</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08729782787483993</v>
+        <v>0.0872271081943902</v>
       </c>
       <c r="C13">
-        <v>974.1200554148197</v>
+        <v>965.3309654512108</v>
       </c>
       <c r="D13">
-        <v>986.4230554148197</v>
+        <v>988.1069654512108</v>
       </c>
       <c r="E13">
-        <v>-332.897</v>
+        <v>-322.424</v>
       </c>
       <c r="F13">
-        <v>115.203</v>
+        <v>125.676</v>
       </c>
       <c r="G13">
         <v>102.9</v>
@@ -2359,28 +2359,28 @@
         <v>109.325</v>
       </c>
       <c r="M13">
-        <v>5.794710900000001</v>
+        <v>6.3215028</v>
       </c>
       <c r="N13">
-        <v>103.5302891</v>
+        <v>103.0034972</v>
       </c>
       <c r="O13">
-        <v>12.9412861375</v>
+        <v>12.87543715</v>
       </c>
       <c r="P13">
-        <v>90.58900296249999</v>
+        <v>90.12806004999999</v>
       </c>
       <c r="Q13">
-        <v>104.8890029625</v>
+        <v>104.42806005</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09264769985937071</v>
+        <v>0.09312000931180704</v>
       </c>
       <c r="T13">
-        <v>0.9131488678370285</v>
+        <v>0.9223550581741342</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.86634240890257</v>
+        <v>17.29414720816069</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0872271081943902</v>
+        <v>0.08715638851394045</v>
       </c>
       <c r="C14">
-        <v>965.3309654512108</v>
+        <v>956.5476344807811</v>
       </c>
       <c r="D14">
-        <v>988.1069654512108</v>
+        <v>989.7966344807811</v>
       </c>
       <c r="E14">
-        <v>-322.424</v>
+        <v>-311.951</v>
       </c>
       <c r="F14">
-        <v>125.676</v>
+        <v>136.149</v>
       </c>
       <c r="G14">
         <v>102.9</v>
@@ -2441,28 +2441,28 @@
         <v>109.325</v>
       </c>
       <c r="M14">
-        <v>6.3215028</v>
+        <v>6.848294700000001</v>
       </c>
       <c r="N14">
-        <v>103.0034972</v>
+        <v>102.4767053</v>
       </c>
       <c r="O14">
-        <v>12.87543715</v>
+        <v>12.8095881625</v>
       </c>
       <c r="P14">
-        <v>90.12806004999999</v>
+        <v>89.66711713749999</v>
       </c>
       <c r="Q14">
-        <v>104.42806005</v>
+        <v>103.9671171375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09312000931180704</v>
+        <v>0.09360317645280512</v>
       </c>
       <c r="T14">
-        <v>0.9223550581741342</v>
+        <v>0.9317728850707135</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.29414720816069</v>
+        <v>15.96382819214833</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08715638851394045</v>
+        <v>0.08708566883349071</v>
       </c>
       <c r="C15">
-        <v>956.5476344807811</v>
+        <v>947.7700920978784</v>
       </c>
       <c r="D15">
-        <v>989.7966344807811</v>
+        <v>991.4920920978784</v>
       </c>
       <c r="E15">
-        <v>-311.951</v>
+        <v>-301.478</v>
       </c>
       <c r="F15">
-        <v>136.149</v>
+        <v>146.622</v>
       </c>
       <c r="G15">
         <v>102.9</v>
@@ -2523,28 +2523,28 @@
         <v>109.325</v>
       </c>
       <c r="M15">
-        <v>6.848294700000001</v>
+        <v>7.375086600000002</v>
       </c>
       <c r="N15">
-        <v>102.4767053</v>
+        <v>101.9499134</v>
       </c>
       <c r="O15">
-        <v>12.8095881625</v>
+        <v>12.743739175</v>
       </c>
       <c r="P15">
-        <v>89.66711713749999</v>
+        <v>89.20617422499998</v>
       </c>
       <c r="Q15">
-        <v>103.9671171375</v>
+        <v>103.506174225</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09360317645280512</v>
+        <v>0.0940975800389427</v>
       </c>
       <c r="T15">
-        <v>0.9317728850707135</v>
+        <v>0.9414097311974459</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.96382819214833</v>
+        <v>14.82355474985202</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08708566883349071</v>
+        <v>0.087014949153041</v>
       </c>
       <c r="C16">
-        <v>947.7700920978784</v>
+        <v>938.9983680999721</v>
       </c>
       <c r="D16">
-        <v>991.4920920978784</v>
+        <v>993.1933680999721</v>
       </c>
       <c r="E16">
-        <v>-301.478</v>
+        <v>-291.005</v>
       </c>
       <c r="F16">
-        <v>146.622</v>
+        <v>157.0950000000001</v>
       </c>
       <c r="G16">
         <v>102.9</v>
@@ -2605,28 +2605,28 @@
         <v>109.325</v>
       </c>
       <c r="M16">
-        <v>7.375086600000002</v>
+        <v>7.901878500000002</v>
       </c>
       <c r="N16">
-        <v>101.9499134</v>
+        <v>101.4231215</v>
       </c>
       <c r="O16">
-        <v>12.743739175</v>
+        <v>12.6778901875</v>
       </c>
       <c r="P16">
-        <v>89.20617422499998</v>
+        <v>88.74523131249998</v>
       </c>
       <c r="Q16">
-        <v>103.506174225</v>
+        <v>103.0452313125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0940975800389427</v>
+        <v>0.09460361665063646</v>
       </c>
       <c r="T16">
-        <v>0.9414097311974459</v>
+        <v>0.9512733266448073</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.82355474985202</v>
+        <v>13.83531776652855</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08701494915304099</v>
+        <v>0.08694422947259126</v>
       </c>
       <c r="C17">
-        <v>938.9983680999724</v>
+        <v>930.232492489399</v>
       </c>
       <c r="D17">
-        <v>993.1933680999723</v>
+        <v>994.900492489399</v>
       </c>
       <c r="E17">
-        <v>-291.005</v>
+        <v>-280.532</v>
       </c>
       <c r="F17">
-        <v>157.095</v>
+        <v>167.568</v>
       </c>
       <c r="G17">
         <v>102.9</v>
@@ -2687,28 +2687,28 @@
         <v>109.325</v>
       </c>
       <c r="M17">
-        <v>7.901878500000001</v>
+        <v>8.428670400000001</v>
       </c>
       <c r="N17">
-        <v>101.4231215</v>
+        <v>100.8963296</v>
       </c>
       <c r="O17">
-        <v>12.6778901875</v>
+        <v>12.6120412</v>
       </c>
       <c r="P17">
-        <v>88.7452313125</v>
+        <v>88.28428839999999</v>
       </c>
       <c r="Q17">
-        <v>103.0452313125</v>
+        <v>102.5842884</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09460361665063646</v>
+        <v>0.09512170175308483</v>
       </c>
       <c r="T17">
-        <v>0.9512733266448071</v>
+        <v>0.9613717696028201</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.83531776652855</v>
+        <v>12.97061040612052</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08694422947259126</v>
+        <v>0.08709663479214153</v>
       </c>
       <c r="C18">
-        <v>930.232492489399</v>
+        <v>916.0878100813346</v>
       </c>
       <c r="D18">
-        <v>994.900492489399</v>
+        <v>991.2288100813346</v>
       </c>
       <c r="E18">
-        <v>-280.532</v>
+        <v>-270.059</v>
       </c>
       <c r="F18">
-        <v>167.568</v>
+        <v>178.0410000000001</v>
       </c>
       <c r="G18">
         <v>102.9</v>
@@ -2769,45 +2769,45 @@
         <v>109.325</v>
       </c>
       <c r="M18">
-        <v>8.428670400000001</v>
+        <v>9.222523800000003</v>
       </c>
       <c r="N18">
-        <v>100.8963296</v>
+        <v>100.1024762</v>
       </c>
       <c r="O18">
-        <v>12.6120412</v>
+        <v>12.512809525</v>
       </c>
       <c r="P18">
-        <v>88.28428839999999</v>
+        <v>87.58966667499999</v>
       </c>
       <c r="Q18">
-        <v>102.5842884</v>
+        <v>101.889666675</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09512170175308483</v>
+        <v>0.09565227083390546</v>
       </c>
       <c r="T18">
-        <v>0.9613717696028201</v>
+        <v>0.9717135485357248</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.97061040612052</v>
+        <v>11.85413042794207</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08709663479214153</v>
+        <v>0.08703904011169178</v>
       </c>
       <c r="C19">
-        <v>916.0878100813346</v>
+        <v>906.9991659347829</v>
       </c>
       <c r="D19">
-        <v>991.2288100813346</v>
+        <v>992.613165934783</v>
       </c>
       <c r="E19">
-        <v>-270.059</v>
+        <v>-259.586</v>
       </c>
       <c r="F19">
-        <v>178.0410000000001</v>
+        <v>188.5140000000001</v>
       </c>
       <c r="G19">
         <v>102.9</v>
@@ -2851,28 +2851,28 @@
         <v>109.325</v>
       </c>
       <c r="M19">
-        <v>9.222523800000003</v>
+        <v>9.765025200000004</v>
       </c>
       <c r="N19">
-        <v>100.1024762</v>
+        <v>99.55997479999999</v>
       </c>
       <c r="O19">
-        <v>12.512809525</v>
+        <v>12.44499685</v>
       </c>
       <c r="P19">
-        <v>87.58966667499999</v>
+        <v>87.11497795</v>
       </c>
       <c r="Q19">
-        <v>101.889666675</v>
+        <v>101.41497795</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09565227083390546</v>
+        <v>0.09619578062401438</v>
       </c>
       <c r="T19">
-        <v>0.9717135485357248</v>
+        <v>0.9823075659791881</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.85413042794207</v>
+        <v>11.19556762638974</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08703904011169179</v>
+        <v>0.08698144543124206</v>
       </c>
       <c r="C20">
-        <v>906.9991659347828</v>
+        <v>897.9143939948603</v>
       </c>
       <c r="D20">
-        <v>992.6131659347827</v>
+        <v>994.0013939948605</v>
       </c>
       <c r="E20">
-        <v>-259.586</v>
+        <v>-249.113</v>
       </c>
       <c r="F20">
-        <v>188.514</v>
+        <v>198.987</v>
       </c>
       <c r="G20">
         <v>102.9</v>
@@ -2933,28 +2933,28 @@
         <v>109.325</v>
       </c>
       <c r="M20">
-        <v>9.765025200000002</v>
+        <v>10.3075266</v>
       </c>
       <c r="N20">
-        <v>99.55997479999999</v>
+        <v>99.01747339999999</v>
       </c>
       <c r="O20">
-        <v>12.44499685</v>
+        <v>12.377184175</v>
       </c>
       <c r="P20">
-        <v>87.11497795</v>
+        <v>86.64028922499999</v>
       </c>
       <c r="Q20">
-        <v>101.41497795</v>
+        <v>100.940289225</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09619578062401438</v>
+        <v>0.0967527104089408</v>
       </c>
       <c r="T20">
-        <v>0.9823075659791881</v>
+        <v>0.9931631641002677</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.19556762638974</v>
+        <v>10.6063272250008</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08698144543124206</v>
+        <v>0.08692385075079234</v>
       </c>
       <c r="C21">
-        <v>897.9143939948603</v>
+        <v>888.8335105308493</v>
       </c>
       <c r="D21">
-        <v>994.0013939948605</v>
+        <v>995.3935105308492</v>
       </c>
       <c r="E21">
-        <v>-249.113</v>
+        <v>-238.64</v>
       </c>
       <c r="F21">
-        <v>198.987</v>
+        <v>209.46</v>
       </c>
       <c r="G21">
         <v>102.9</v>
@@ -3015,28 +3015,28 @@
         <v>109.325</v>
       </c>
       <c r="M21">
-        <v>10.3075266</v>
+        <v>10.850028</v>
       </c>
       <c r="N21">
-        <v>99.01747339999999</v>
+        <v>98.47497199999998</v>
       </c>
       <c r="O21">
-        <v>12.377184175</v>
+        <v>12.3093715</v>
       </c>
       <c r="P21">
-        <v>86.64028922499999</v>
+        <v>86.16560049999998</v>
       </c>
       <c r="Q21">
-        <v>100.940289225</v>
+        <v>100.4656005</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0967527104089408</v>
+        <v>0.09732356343849041</v>
       </c>
       <c r="T21">
-        <v>0.9931631641002677</v>
+        <v>1.004290152174375</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.6063272250008</v>
+        <v>10.07601086375076</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08692385075079234</v>
+        <v>0.0871786310703426</v>
       </c>
       <c r="C22">
-        <v>888.8335105308493</v>
+        <v>872.2315818995423</v>
       </c>
       <c r="D22">
-        <v>995.3935105308492</v>
+        <v>989.2645818995423</v>
       </c>
       <c r="E22">
-        <v>-238.64</v>
+        <v>-228.167</v>
       </c>
       <c r="F22">
-        <v>209.46</v>
+        <v>219.933</v>
       </c>
       <c r="G22">
         <v>102.9</v>
@@ -3097,45 +3097,45 @@
         <v>109.325</v>
       </c>
       <c r="M22">
-        <v>10.850028</v>
+        <v>11.7664155</v>
       </c>
       <c r="N22">
-        <v>98.47497199999998</v>
+        <v>97.55858449999998</v>
       </c>
       <c r="O22">
-        <v>12.3093715</v>
+        <v>12.1948230625</v>
       </c>
       <c r="P22">
-        <v>86.16560049999998</v>
+        <v>85.36376143749999</v>
       </c>
       <c r="Q22">
-        <v>100.4656005</v>
+        <v>99.6637614375</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09732356343849041</v>
+        <v>0.09790886844347164</v>
       </c>
       <c r="T22">
-        <v>1.004290152174375</v>
+        <v>1.015698836149092</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.07601086375076</v>
+        <v>9.291274815172043</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08717863107034259</v>
+        <v>0.08713591138989285</v>
       </c>
       <c r="C23">
-        <v>872.2315818995426</v>
+        <v>862.780963296202</v>
       </c>
       <c r="D23">
-        <v>989.2645818995426</v>
+        <v>990.286963296202</v>
       </c>
       <c r="E23">
-        <v>-228.167</v>
+        <v>-217.694</v>
       </c>
       <c r="F23">
-        <v>219.933</v>
+        <v>230.406</v>
       </c>
       <c r="G23">
         <v>102.9</v>
@@ -3179,28 +3179,28 @@
         <v>109.325</v>
       </c>
       <c r="M23">
-        <v>11.7664155</v>
+        <v>12.326721</v>
       </c>
       <c r="N23">
-        <v>97.55858449999999</v>
+        <v>96.99827899999998</v>
       </c>
       <c r="O23">
-        <v>12.1948230625</v>
+        <v>12.124784875</v>
       </c>
       <c r="P23">
-        <v>85.36376143749999</v>
+        <v>84.87349412499998</v>
       </c>
       <c r="Q23">
-        <v>99.6637614375</v>
+        <v>99.17349412499999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09790886844347163</v>
+        <v>0.0985091812690934</v>
       </c>
       <c r="T23">
-        <v>1.015698836149092</v>
+        <v>1.027400050482135</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.291274815172045</v>
+        <v>8.868944141755133</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08713591138989285</v>
+        <v>0.0870931917094431</v>
       </c>
       <c r="C24">
-        <v>862.780963296202</v>
+        <v>853.3324600927502</v>
       </c>
       <c r="D24">
-        <v>990.286963296202</v>
+        <v>991.3114600927502</v>
       </c>
       <c r="E24">
-        <v>-217.694</v>
+        <v>-207.221</v>
       </c>
       <c r="F24">
-        <v>230.406</v>
+        <v>240.879</v>
       </c>
       <c r="G24">
         <v>102.9</v>
@@ -3261,28 +3261,28 @@
         <v>109.325</v>
       </c>
       <c r="M24">
-        <v>12.326721</v>
+        <v>12.8870265</v>
       </c>
       <c r="N24">
-        <v>96.99827899999998</v>
+        <v>96.43797349999998</v>
       </c>
       <c r="O24">
-        <v>12.124784875</v>
+        <v>12.0547466875</v>
       </c>
       <c r="P24">
-        <v>84.87349412499998</v>
+        <v>84.38322681249998</v>
       </c>
       <c r="Q24">
-        <v>99.17349412499999</v>
+        <v>98.6832268125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0985091812690934</v>
+        <v>0.0991250866356404</v>
       </c>
       <c r="T24">
-        <v>1.027400050482135</v>
+        <v>1.039405192460192</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.868944141755133</v>
+        <v>8.4833378747223</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0870931917094431</v>
+        <v>0.08705047202899338</v>
       </c>
       <c r="C25">
-        <v>853.3324600927502</v>
+        <v>843.8860788614163</v>
       </c>
       <c r="D25">
-        <v>991.3114600927502</v>
+        <v>992.3380788614163</v>
       </c>
       <c r="E25">
-        <v>-207.221</v>
+        <v>-196.748</v>
       </c>
       <c r="F25">
-        <v>240.879</v>
+        <v>251.3520000000001</v>
       </c>
       <c r="G25">
         <v>102.9</v>
@@ -3343,28 +3343,28 @@
         <v>109.325</v>
       </c>
       <c r="M25">
-        <v>12.8870265</v>
+        <v>13.447332</v>
       </c>
       <c r="N25">
-        <v>96.43797349999998</v>
+        <v>95.87766799999999</v>
       </c>
       <c r="O25">
-        <v>12.0547466875</v>
+        <v>11.9847085</v>
       </c>
       <c r="P25">
-        <v>84.38322681249998</v>
+        <v>83.89295949999999</v>
       </c>
       <c r="Q25">
-        <v>98.6832268125</v>
+        <v>98.1929595</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0991250866356404</v>
+        <v>0.0997572000381492</v>
       </c>
       <c r="T25">
-        <v>1.039405192460192</v>
+        <v>1.051726259227145</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.4833378747223</v>
+        <v>8.129865463275538</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08705047202899338</v>
+        <v>0.08700775234854365</v>
       </c>
       <c r="C26">
-        <v>843.8860788614163</v>
+        <v>834.4418262016861</v>
       </c>
       <c r="D26">
-        <v>992.3380788614163</v>
+        <v>993.3668262016862</v>
       </c>
       <c r="E26">
-        <v>-196.748</v>
+        <v>-186.275</v>
       </c>
       <c r="F26">
-        <v>251.352</v>
+        <v>261.825</v>
       </c>
       <c r="G26">
         <v>102.9</v>
@@ -3425,28 +3425,28 @@
         <v>109.325</v>
       </c>
       <c r="M26">
-        <v>13.447332</v>
+        <v>14.0076375</v>
       </c>
       <c r="N26">
-        <v>95.87766799999999</v>
+        <v>95.31736249999999</v>
       </c>
       <c r="O26">
-        <v>11.9847085</v>
+        <v>11.9146703125</v>
       </c>
       <c r="P26">
-        <v>83.89295949999999</v>
+        <v>83.40269218749999</v>
       </c>
       <c r="Q26">
-        <v>98.1929595</v>
+        <v>97.70269218750001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09975720003814918</v>
+        <v>0.1004061697980582</v>
       </c>
       <c r="T26">
-        <v>1.051726259227145</v>
+        <v>1.064375887774551</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.129865463275539</v>
+        <v>7.804670844744518</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08700775234854365</v>
+        <v>0.08714703266809391</v>
       </c>
       <c r="C27">
-        <v>834.4418262016861</v>
+        <v>820.6226018161387</v>
       </c>
       <c r="D27">
-        <v>993.3668262016862</v>
+        <v>990.0206018161388</v>
       </c>
       <c r="E27">
-        <v>-186.275</v>
+        <v>-175.802</v>
       </c>
       <c r="F27">
-        <v>261.825</v>
+        <v>272.2980000000001</v>
       </c>
       <c r="G27">
         <v>102.9</v>
@@ -3507,45 +3507,45 @@
         <v>109.325</v>
       </c>
       <c r="M27">
-        <v>14.0076375</v>
+        <v>14.7857814</v>
       </c>
       <c r="N27">
-        <v>95.31736249999999</v>
+        <v>94.53921859999998</v>
       </c>
       <c r="O27">
-        <v>11.9146703125</v>
+        <v>11.817402325</v>
       </c>
       <c r="P27">
-        <v>83.40269218749999</v>
+        <v>82.72181627499998</v>
       </c>
       <c r="Q27">
-        <v>97.70269218750001</v>
+        <v>97.02181627499999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1004061697980582</v>
+        <v>0.101072679281208</v>
       </c>
       <c r="T27">
-        <v>1.064375887774551</v>
+        <v>1.077367398174589</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.804670844744518</v>
+        <v>7.393927790654335</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08714703266809391</v>
+        <v>0.08711131298764418</v>
       </c>
       <c r="C28">
-        <v>820.6226018161387</v>
+        <v>811.0056196228371</v>
       </c>
       <c r="D28">
-        <v>990.0206018161388</v>
+        <v>990.8766196228372</v>
       </c>
       <c r="E28">
-        <v>-175.802</v>
+        <v>-165.329</v>
       </c>
       <c r="F28">
-        <v>272.2980000000001</v>
+        <v>282.7710000000001</v>
       </c>
       <c r="G28">
         <v>102.9</v>
@@ -3589,28 +3589,28 @@
         <v>109.325</v>
       </c>
       <c r="M28">
-        <v>14.7857814</v>
+        <v>15.3544653</v>
       </c>
       <c r="N28">
-        <v>94.53921859999998</v>
+        <v>93.97053469999999</v>
       </c>
       <c r="O28">
-        <v>11.817402325</v>
+        <v>11.7463168375</v>
       </c>
       <c r="P28">
-        <v>82.72181627499998</v>
+        <v>82.22421786249998</v>
       </c>
       <c r="Q28">
-        <v>97.02181627499999</v>
+        <v>96.5242178625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.101072679281208</v>
+        <v>0.1017574492981427</v>
       </c>
       <c r="T28">
-        <v>1.077367398174589</v>
+        <v>1.090714840366409</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.393927790654335</v>
+        <v>7.120078613222693</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08711131298764418</v>
+        <v>0.08707559330719444</v>
       </c>
       <c r="C29">
-        <v>811.0056196228371</v>
+        <v>801.3901190161137</v>
       </c>
       <c r="D29">
-        <v>990.8766196228372</v>
+        <v>991.7341190161138</v>
       </c>
       <c r="E29">
-        <v>-165.329</v>
+        <v>-154.8559999999999</v>
       </c>
       <c r="F29">
-        <v>282.7710000000001</v>
+        <v>293.2440000000001</v>
       </c>
       <c r="G29">
         <v>102.9</v>
@@ -3671,28 +3671,28 @@
         <v>109.325</v>
       </c>
       <c r="M29">
-        <v>15.3544653</v>
+        <v>15.9231492</v>
       </c>
       <c r="N29">
-        <v>93.97053469999999</v>
+        <v>93.40185079999998</v>
       </c>
       <c r="O29">
-        <v>11.7463168375</v>
+        <v>11.67523135</v>
       </c>
       <c r="P29">
-        <v>82.22421786249998</v>
+        <v>81.72661944999999</v>
       </c>
       <c r="Q29">
-        <v>96.5242178625</v>
+        <v>96.02661945</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1017574492981427</v>
+        <v>0.1024612407044367</v>
       </c>
       <c r="T29">
-        <v>1.090714840366409</v>
+        <v>1.104433044841335</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.120078613222693</v>
+        <v>6.865790091321882</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08707559330719444</v>
+        <v>0.08703987362674472</v>
       </c>
       <c r="C30">
-        <v>801.3901190161137</v>
+        <v>791.7761038457709</v>
       </c>
       <c r="D30">
-        <v>991.7341190161138</v>
+        <v>992.593103845771</v>
       </c>
       <c r="E30">
-        <v>-154.8559999999999</v>
+        <v>-144.3829999999999</v>
       </c>
       <c r="F30">
-        <v>293.2440000000001</v>
+        <v>303.7170000000001</v>
       </c>
       <c r="G30">
         <v>102.9</v>
@@ -3753,28 +3753,28 @@
         <v>109.325</v>
       </c>
       <c r="M30">
-        <v>15.9231492</v>
+        <v>16.4918331</v>
       </c>
       <c r="N30">
-        <v>93.40185079999998</v>
+        <v>92.83316689999998</v>
       </c>
       <c r="O30">
-        <v>11.67523135</v>
+        <v>11.6041458625</v>
       </c>
       <c r="P30">
-        <v>81.72661944999999</v>
+        <v>81.22902103749999</v>
       </c>
       <c r="Q30">
-        <v>96.02661945</v>
+        <v>95.5290210375</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1024612407044367</v>
+        <v>0.1031848572207672</v>
       </c>
       <c r="T30">
-        <v>1.104433044841335</v>
+        <v>1.118537677611329</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.865790091321882</v>
+        <v>6.629038708862507</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08703987362674472</v>
+        <v>0.08700415394629497</v>
       </c>
       <c r="C31">
-        <v>791.7761038457709</v>
+        <v>782.1635779749618</v>
       </c>
       <c r="D31">
-        <v>992.593103845771</v>
+        <v>993.4535779749617</v>
       </c>
       <c r="E31">
-        <v>-144.383</v>
+        <v>-133.91</v>
       </c>
       <c r="F31">
-        <v>303.717</v>
+        <v>314.1900000000001</v>
       </c>
       <c r="G31">
         <v>102.9</v>
@@ -3835,28 +3835,28 @@
         <v>109.325</v>
       </c>
       <c r="M31">
-        <v>16.4918331</v>
+        <v>17.060517</v>
       </c>
       <c r="N31">
-        <v>92.83316689999998</v>
+        <v>92.26448299999998</v>
       </c>
       <c r="O31">
-        <v>11.6041458625</v>
+        <v>11.533060375</v>
       </c>
       <c r="P31">
-        <v>81.22902103749999</v>
+        <v>80.73142262499999</v>
       </c>
       <c r="Q31">
-        <v>95.5290210375</v>
+        <v>95.031422625</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1031848572207672</v>
+        <v>0.1039291484947071</v>
       </c>
       <c r="T31">
-        <v>1.118537677611329</v>
+        <v>1.133045299889038</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.629038708862508</v>
+        <v>6.408070751900424</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08700415394629497</v>
+        <v>0.08696843426584525</v>
       </c>
       <c r="C32">
-        <v>782.1635779749618</v>
+        <v>772.5525452802462</v>
       </c>
       <c r="D32">
-        <v>993.4535779749617</v>
+        <v>994.3155452802462</v>
       </c>
       <c r="E32">
-        <v>-133.91</v>
+        <v>-123.437</v>
       </c>
       <c r="F32">
-        <v>314.1900000000001</v>
+        <v>324.6630000000001</v>
       </c>
       <c r="G32">
         <v>102.9</v>
@@ -3917,28 +3917,28 @@
         <v>109.325</v>
       </c>
       <c r="M32">
-        <v>17.060517</v>
+        <v>17.6292009</v>
       </c>
       <c r="N32">
-        <v>92.26448299999998</v>
+        <v>91.69579909999999</v>
       </c>
       <c r="O32">
-        <v>11.533060375</v>
+        <v>11.4619748875</v>
       </c>
       <c r="P32">
-        <v>80.73142262499999</v>
+        <v>80.2338242125</v>
       </c>
       <c r="Q32">
-        <v>95.031422625</v>
+        <v>94.53382421250001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1039291484947071</v>
+        <v>0.1046950134287612</v>
       </c>
       <c r="T32">
-        <v>1.133045299889038</v>
+        <v>1.147973432957405</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.408070751900424</v>
+        <v>6.201358792161701</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08696843426584525</v>
+        <v>0.08721271458539551</v>
       </c>
       <c r="C33">
-        <v>772.5525452802462</v>
+        <v>756.2143968212143</v>
       </c>
       <c r="D33">
-        <v>994.3155452802462</v>
+        <v>988.4503968212144</v>
       </c>
       <c r="E33">
-        <v>-123.437</v>
+        <v>-112.9639999999999</v>
       </c>
       <c r="F33">
-        <v>324.6630000000001</v>
+        <v>335.1360000000001</v>
       </c>
       <c r="G33">
         <v>102.9</v>
@@ -3999,45 +3999,45 @@
         <v>109.325</v>
       </c>
       <c r="M33">
-        <v>17.6292009</v>
+        <v>18.53302080000001</v>
       </c>
       <c r="N33">
-        <v>91.69579909999999</v>
+        <v>90.79197919999999</v>
       </c>
       <c r="O33">
-        <v>11.4619748875</v>
+        <v>11.3489974</v>
       </c>
       <c r="P33">
-        <v>80.2338242125</v>
+        <v>79.44298179999998</v>
       </c>
       <c r="Q33">
-        <v>94.53382421250001</v>
+        <v>93.7429818</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1046950134287612</v>
+        <v>0.1054834038020522</v>
       </c>
       <c r="T33">
-        <v>1.147973432957405</v>
+        <v>1.163340628763077</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.201358792161701</v>
+        <v>5.898930410740161</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08721271458539551</v>
+        <v>0.08718574490494579</v>
       </c>
       <c r="C34">
-        <v>756.2143968212143</v>
+        <v>746.3855362804384</v>
       </c>
       <c r="D34">
-        <v>988.4503968212144</v>
+        <v>989.0945362804385</v>
       </c>
       <c r="E34">
-        <v>-112.9639999999999</v>
+        <v>-102.4909999999999</v>
       </c>
       <c r="F34">
-        <v>335.1360000000001</v>
+        <v>345.6090000000001</v>
       </c>
       <c r="G34">
         <v>102.9</v>
@@ -4081,28 +4081,28 @@
         <v>109.325</v>
       </c>
       <c r="M34">
-        <v>18.53302080000001</v>
+        <v>19.11217770000001</v>
       </c>
       <c r="N34">
-        <v>90.79197919999999</v>
+        <v>90.21282229999998</v>
       </c>
       <c r="O34">
-        <v>11.3489974</v>
+        <v>11.2766027875</v>
       </c>
       <c r="P34">
-        <v>79.44298179999998</v>
+        <v>78.93621951249999</v>
       </c>
       <c r="Q34">
-        <v>93.7429818</v>
+        <v>93.2362195125</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1054834038020522</v>
+        <v>0.106295328216337</v>
       </c>
       <c r="T34">
-        <v>1.163340628763077</v>
+        <v>1.179166546831604</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.898930410740161</v>
+        <v>5.720174943748035</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08718574490494579</v>
+        <v>0.08715877522449604</v>
       </c>
       <c r="C35">
-        <v>746.3855362804384</v>
+        <v>736.5575158146071</v>
       </c>
       <c r="D35">
-        <v>989.0945362804385</v>
+        <v>989.7395158146071</v>
       </c>
       <c r="E35">
-        <v>-102.4909999999999</v>
+        <v>-92.01799999999992</v>
       </c>
       <c r="F35">
-        <v>345.6090000000001</v>
+        <v>356.0820000000001</v>
       </c>
       <c r="G35">
         <v>102.9</v>
@@ -4163,28 +4163,28 @@
         <v>109.325</v>
       </c>
       <c r="M35">
-        <v>19.11217770000001</v>
+        <v>19.69133460000001</v>
       </c>
       <c r="N35">
-        <v>90.21282229999998</v>
+        <v>89.63366539999998</v>
       </c>
       <c r="O35">
-        <v>11.2766027875</v>
+        <v>11.204208175</v>
       </c>
       <c r="P35">
-        <v>78.93621951249999</v>
+        <v>78.42945722499999</v>
       </c>
       <c r="Q35">
-        <v>93.2362195125</v>
+        <v>92.729457225</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.106295328216337</v>
+        <v>0.1071318564007516</v>
       </c>
       <c r="T35">
-        <v>1.179166546831604</v>
+        <v>1.195472038174936</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.720174943748035</v>
+        <v>5.551934504226034</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08715877522449604</v>
+        <v>0.08713180554404631</v>
       </c>
       <c r="C36">
-        <v>736.5575158146071</v>
+        <v>726.7303370682066</v>
       </c>
       <c r="D36">
-        <v>989.7395158146071</v>
+        <v>990.3853370682067</v>
       </c>
       <c r="E36">
-        <v>-92.01799999999992</v>
+        <v>-81.5449999999999</v>
       </c>
       <c r="F36">
-        <v>356.0820000000001</v>
+        <v>366.5550000000001</v>
       </c>
       <c r="G36">
         <v>102.9</v>
@@ -4245,28 +4245,28 @@
         <v>109.325</v>
       </c>
       <c r="M36">
-        <v>19.69133460000001</v>
+        <v>20.27049150000001</v>
       </c>
       <c r="N36">
-        <v>89.63366539999998</v>
+        <v>89.05450849999998</v>
       </c>
       <c r="O36">
-        <v>11.204208175</v>
+        <v>11.1318135625</v>
       </c>
       <c r="P36">
-        <v>78.42945722499999</v>
+        <v>77.92269493749998</v>
       </c>
       <c r="Q36">
-        <v>92.729457225</v>
+        <v>92.22269493749999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1071318564007516</v>
+        <v>0.1079941239139174</v>
       </c>
       <c r="T36">
-        <v>1.195472038174936</v>
+        <v>1.212279236944215</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.551934504226034</v>
+        <v>5.393307804105291</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08713180554404631</v>
+        <v>0.08710483586359657</v>
       </c>
       <c r="C37">
-        <v>726.7303370682066</v>
+        <v>716.9040016900209</v>
       </c>
       <c r="D37">
-        <v>990.3853370682067</v>
+        <v>991.032001690021</v>
       </c>
       <c r="E37">
-        <v>-81.5449999999999</v>
+        <v>-71.07199999999989</v>
       </c>
       <c r="F37">
-        <v>366.5550000000001</v>
+        <v>377.0280000000001</v>
       </c>
       <c r="G37">
         <v>102.9</v>
@@ -4327,28 +4327,28 @@
         <v>109.325</v>
       </c>
       <c r="M37">
-        <v>20.27049150000001</v>
+        <v>20.84964840000001</v>
       </c>
       <c r="N37">
-        <v>89.05450849999998</v>
+        <v>88.47535159999998</v>
       </c>
       <c r="O37">
-        <v>11.1318135625</v>
+        <v>11.05941895</v>
       </c>
       <c r="P37">
-        <v>77.92269493749998</v>
+        <v>77.41593264999999</v>
       </c>
       <c r="Q37">
-        <v>92.22269493749999</v>
+        <v>91.71593265</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1079941239139174</v>
+        <v>0.1088833372868697</v>
       </c>
       <c r="T37">
-        <v>1.212279236944215</v>
+        <v>1.229611660675035</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.393307804105291</v>
+        <v>5.243493698435699</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08710483586359659</v>
+        <v>0.08707786618314686</v>
       </c>
       <c r="C38">
-        <v>716.9040016900208</v>
+        <v>707.0785113331416</v>
       </c>
       <c r="D38">
-        <v>991.0320016900207</v>
+        <v>991.6795113331416</v>
       </c>
       <c r="E38">
-        <v>-71.07199999999995</v>
+        <v>-60.59899999999993</v>
       </c>
       <c r="F38">
-        <v>377.0280000000001</v>
+        <v>387.5010000000001</v>
       </c>
       <c r="G38">
         <v>102.9</v>
@@ -4409,28 +4409,28 @@
         <v>109.325</v>
       </c>
       <c r="M38">
-        <v>20.84964840000001</v>
+        <v>21.4288053</v>
       </c>
       <c r="N38">
-        <v>88.47535159999998</v>
+        <v>87.89619469999998</v>
       </c>
       <c r="O38">
-        <v>11.05941895</v>
+        <v>10.9870243375</v>
       </c>
       <c r="P38">
-        <v>77.41593264999999</v>
+        <v>76.90917036249998</v>
       </c>
       <c r="Q38">
-        <v>91.71593265</v>
+        <v>91.20917036249999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1088833372868697</v>
+        <v>0.1098007796557887</v>
       </c>
       <c r="T38">
-        <v>1.229611660675035</v>
+        <v>1.24749432007985</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.243493698435699</v>
+        <v>5.101777652532032</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08707786618314686</v>
+        <v>0.08705089650269709</v>
       </c>
       <c r="C39">
-        <v>707.0785113331416</v>
+        <v>697.2538676549849</v>
       </c>
       <c r="D39">
-        <v>991.6795113331416</v>
+        <v>992.3278676549849</v>
       </c>
       <c r="E39">
-        <v>-60.59899999999993</v>
+        <v>-50.12599999999998</v>
       </c>
       <c r="F39">
-        <v>387.5010000000001</v>
+        <v>397.974</v>
       </c>
       <c r="G39">
         <v>102.9</v>
@@ -4491,28 +4491,28 @@
         <v>109.325</v>
       </c>
       <c r="M39">
-        <v>21.4288053</v>
+        <v>22.00796220000001</v>
       </c>
       <c r="N39">
-        <v>87.89619469999998</v>
+        <v>87.31703779999998</v>
       </c>
       <c r="O39">
-        <v>10.9870243375</v>
+        <v>10.914629725</v>
       </c>
       <c r="P39">
-        <v>76.90917036249998</v>
+        <v>76.40240807499998</v>
       </c>
       <c r="Q39">
-        <v>91.20917036249999</v>
+        <v>90.70240807499999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1098007796557887</v>
+        <v>0.110747816939834</v>
       </c>
       <c r="T39">
-        <v>1.24749432007985</v>
+        <v>1.265953839465465</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.101777652532032</v>
+        <v>4.967520345886452</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08705089650269709</v>
+        <v>0.08702392682224737</v>
       </c>
       <c r="C40">
-        <v>697.2538676549849</v>
+        <v>687.4300723173017</v>
       </c>
       <c r="D40">
-        <v>992.3278676549849</v>
+        <v>992.9770723173018</v>
       </c>
       <c r="E40">
-        <v>-50.12599999999998</v>
+        <v>-39.65299999999996</v>
       </c>
       <c r="F40">
-        <v>397.974</v>
+        <v>408.4470000000001</v>
       </c>
       <c r="G40">
         <v>102.9</v>
@@ -4573,28 +4573,28 @@
         <v>109.325</v>
       </c>
       <c r="M40">
-        <v>22.00796220000001</v>
+        <v>22.5871191</v>
       </c>
       <c r="N40">
-        <v>87.31703779999998</v>
+        <v>86.73788089999999</v>
       </c>
       <c r="O40">
-        <v>10.914629725</v>
+        <v>10.8422351125</v>
       </c>
       <c r="P40">
-        <v>76.40240807499998</v>
+        <v>75.8956457875</v>
       </c>
       <c r="Q40">
-        <v>90.70240807499999</v>
+        <v>90.19564578750001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.110747816939834</v>
+        <v>0.111725904626635</v>
       </c>
       <c r="T40">
-        <v>1.265953839465465</v>
+        <v>1.28501858899487</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.967520345886452</v>
+        <v>4.840148029325261</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08702392682224737</v>
+        <v>0.08699695714179764</v>
       </c>
       <c r="C41">
-        <v>687.4300723173017</v>
+        <v>677.607126986197</v>
       </c>
       <c r="D41">
-        <v>992.9770723173018</v>
+        <v>993.627126986197</v>
       </c>
       <c r="E41">
-        <v>-39.65299999999996</v>
+        <v>-29.17999999999995</v>
       </c>
       <c r="F41">
-        <v>408.4470000000001</v>
+        <v>418.9200000000001</v>
       </c>
       <c r="G41">
         <v>102.9</v>
@@ -4655,28 +4655,28 @@
         <v>109.325</v>
       </c>
       <c r="M41">
-        <v>22.5871191</v>
+        <v>23.166276</v>
       </c>
       <c r="N41">
-        <v>86.73788089999999</v>
+        <v>86.15872399999998</v>
       </c>
       <c r="O41">
-        <v>10.8422351125</v>
+        <v>10.7698405</v>
       </c>
       <c r="P41">
-        <v>75.8956457875</v>
+        <v>75.38888349999998</v>
       </c>
       <c r="Q41">
-        <v>90.19564578750001</v>
+        <v>89.68888349999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.111725904626635</v>
+        <v>0.1127365952363294</v>
       </c>
       <c r="T41">
-        <v>1.28501858899487</v>
+        <v>1.304718830175256</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.840148029325261</v>
+        <v>4.71914432859213</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08699695714179764</v>
+        <v>0.0869699874613479</v>
       </c>
       <c r="C42">
-        <v>677.607126986197</v>
+        <v>667.7850333321408</v>
       </c>
       <c r="D42">
-        <v>993.627126986197</v>
+        <v>994.2780333321407</v>
       </c>
       <c r="E42">
-        <v>-29.17999999999995</v>
+        <v>-18.70699999999994</v>
       </c>
       <c r="F42">
-        <v>418.9200000000001</v>
+        <v>429.3930000000001</v>
       </c>
       <c r="G42">
         <v>102.9</v>
@@ -4737,28 +4737,28 @@
         <v>109.325</v>
       </c>
       <c r="M42">
-        <v>23.166276</v>
+        <v>23.7454329</v>
       </c>
       <c r="N42">
-        <v>86.15872399999998</v>
+        <v>85.57956709999999</v>
       </c>
       <c r="O42">
-        <v>10.7698405</v>
+        <v>10.6974458875</v>
       </c>
       <c r="P42">
-        <v>75.38888349999998</v>
+        <v>74.8821212125</v>
       </c>
       <c r="Q42">
-        <v>89.68888349999999</v>
+        <v>89.18212121250001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1127365952363294</v>
+        <v>0.1137815465446575</v>
       </c>
       <c r="T42">
-        <v>1.304718830175256</v>
+        <v>1.325086876141417</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.71914432859213</v>
+        <v>4.604043247406956</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0869699874613479</v>
+        <v>0.08786176778089819</v>
       </c>
       <c r="C43">
-        <v>667.7850333321408</v>
+        <v>636.2316644112358</v>
       </c>
       <c r="D43">
-        <v>994.2780333321407</v>
+        <v>973.1976644112358</v>
       </c>
       <c r="E43">
-        <v>-18.70699999999994</v>
+        <v>-8.233999999999924</v>
       </c>
       <c r="F43">
-        <v>429.3930000000001</v>
+        <v>439.8660000000001</v>
       </c>
       <c r="G43">
         <v>102.9</v>
@@ -4819,45 +4819,45 @@
         <v>109.325</v>
       </c>
       <c r="M43">
-        <v>23.7454329</v>
+        <v>25.42425480000001</v>
       </c>
       <c r="N43">
-        <v>85.57956709999999</v>
+        <v>83.90074519999999</v>
       </c>
       <c r="O43">
-        <v>10.6974458875</v>
+        <v>10.48759315</v>
       </c>
       <c r="P43">
-        <v>74.8821212125</v>
+        <v>73.41315204999999</v>
       </c>
       <c r="Q43">
-        <v>89.18212121250001</v>
+        <v>87.71315205000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1137815465446575</v>
+        <v>0.114862530656721</v>
       </c>
       <c r="T43">
-        <v>1.325086876141417</v>
+        <v>1.346157268520205</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.604043247406956</v>
+        <v>4.300027704253497</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08786176778089819</v>
+        <v>0.08785667310044845</v>
       </c>
       <c r="C44">
-        <v>636.2316644112359</v>
+        <v>625.8765560738208</v>
       </c>
       <c r="D44">
-        <v>973.1976644112358</v>
+        <v>973.3155560738209</v>
       </c>
       <c r="E44">
-        <v>-8.23399999999998</v>
+        <v>2.239000000000033</v>
       </c>
       <c r="F44">
-        <v>439.866</v>
+        <v>450.3390000000001</v>
       </c>
       <c r="G44">
         <v>102.9</v>
@@ -4901,28 +4901,28 @@
         <v>109.325</v>
       </c>
       <c r="M44">
-        <v>25.4242548</v>
+        <v>26.02959420000001</v>
       </c>
       <c r="N44">
-        <v>83.90074519999999</v>
+        <v>83.29540579999998</v>
       </c>
       <c r="O44">
-        <v>10.48759315</v>
+        <v>10.411925725</v>
       </c>
       <c r="P44">
-        <v>73.41315204999999</v>
+        <v>72.88348007499998</v>
       </c>
       <c r="Q44">
-        <v>87.71315205000001</v>
+        <v>87.18348007499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.114862530656721</v>
+        <v>0.1159814440358745</v>
       </c>
       <c r="T44">
-        <v>1.346157268520205</v>
+        <v>1.367966972912283</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.300027704253498</v>
+        <v>4.200027059968532</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08785667310044845</v>
+        <v>0.08785157841999872</v>
       </c>
       <c r="C45">
-        <v>625.8765560738208</v>
+        <v>615.5214763022941</v>
       </c>
       <c r="D45">
-        <v>973.3155560738209</v>
+        <v>973.4334763022941</v>
       </c>
       <c r="E45">
-        <v>2.239000000000033</v>
+        <v>12.71200000000005</v>
       </c>
       <c r="F45">
-        <v>450.3390000000001</v>
+        <v>460.8120000000001</v>
       </c>
       <c r="G45">
         <v>102.9</v>
@@ -4983,28 +4983,28 @@
         <v>109.325</v>
       </c>
       <c r="M45">
-        <v>26.02959420000001</v>
+        <v>26.63493360000001</v>
       </c>
       <c r="N45">
-        <v>83.29540579999998</v>
+        <v>82.69006639999998</v>
       </c>
       <c r="O45">
-        <v>10.411925725</v>
+        <v>10.3362583</v>
       </c>
       <c r="P45">
-        <v>72.88348007499998</v>
+        <v>72.35380809999998</v>
       </c>
       <c r="Q45">
-        <v>87.18348007499999</v>
+        <v>86.65380809999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1159814440358745</v>
+        <v>0.1171403186071406</v>
       </c>
       <c r="T45">
-        <v>1.367966972912283</v>
+        <v>1.390555595318365</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.200027059968532</v>
+        <v>4.104571899514702</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08785157841999872</v>
+        <v>0.08784648373954898</v>
       </c>
       <c r="C46">
-        <v>615.5214763022941</v>
+        <v>605.1664251070397</v>
       </c>
       <c r="D46">
-        <v>973.4334763022941</v>
+        <v>973.5514251070398</v>
       </c>
       <c r="E46">
-        <v>12.71200000000005</v>
+        <v>23.18500000000006</v>
       </c>
       <c r="F46">
-        <v>460.8120000000001</v>
+        <v>471.2850000000001</v>
       </c>
       <c r="G46">
         <v>102.9</v>
@@ -5065,28 +5065,28 @@
         <v>109.325</v>
       </c>
       <c r="M46">
-        <v>26.63493360000001</v>
+        <v>27.24027300000001</v>
       </c>
       <c r="N46">
-        <v>82.69006639999998</v>
+        <v>82.08472699999999</v>
       </c>
       <c r="O46">
-        <v>10.3362583</v>
+        <v>10.260590875</v>
       </c>
       <c r="P46">
-        <v>72.35380809999998</v>
+        <v>71.824136125</v>
       </c>
       <c r="Q46">
-        <v>86.65380809999999</v>
+        <v>86.12413612500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1171403186071406</v>
+        <v>0.1183413340719072</v>
       </c>
       <c r="T46">
-        <v>1.390555595318365</v>
+        <v>1.413965622175576</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.104571899514702</v>
+        <v>4.013359190636598</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08784648373954898</v>
+        <v>0.08925013905909923</v>
       </c>
       <c r="C47">
-        <v>605.1664251070397</v>
+        <v>563.2428781974311</v>
       </c>
       <c r="D47">
-        <v>973.5514251070398</v>
+        <v>942.100878197431</v>
       </c>
       <c r="E47">
-        <v>23.18500000000006</v>
+        <v>33.65800000000007</v>
       </c>
       <c r="F47">
-        <v>471.2850000000001</v>
+        <v>481.7580000000001</v>
       </c>
       <c r="G47">
         <v>102.9</v>
@@ -5147,45 +5147,45 @@
         <v>109.325</v>
       </c>
       <c r="M47">
-        <v>27.24027300000001</v>
+        <v>29.5317654</v>
       </c>
       <c r="N47">
-        <v>82.08472699999999</v>
+        <v>79.79323459999998</v>
       </c>
       <c r="O47">
-        <v>10.260590875</v>
+        <v>9.974154324999997</v>
       </c>
       <c r="P47">
-        <v>71.824136125</v>
+        <v>69.81908027499998</v>
       </c>
       <c r="Q47">
-        <v>86.12413612500001</v>
+        <v>84.11908027499999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1183413340719072</v>
+        <v>0.1195868315909245</v>
       </c>
       <c r="T47">
-        <v>1.413965622175576</v>
+        <v>1.438242687064536</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.013359190636598</v>
+        <v>3.701945973063973</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08925013905909923</v>
+        <v>0.0892756693786495</v>
       </c>
       <c r="C48">
-        <v>563.2428781974311</v>
+        <v>552.2166460836366</v>
       </c>
       <c r="D48">
-        <v>942.100878197431</v>
+        <v>941.5476460836368</v>
       </c>
       <c r="E48">
-        <v>33.65800000000007</v>
+        <v>44.13100000000009</v>
       </c>
       <c r="F48">
-        <v>481.7580000000001</v>
+        <v>492.2310000000001</v>
       </c>
       <c r="G48">
         <v>102.9</v>
@@ -5229,28 +5229,28 @@
         <v>109.325</v>
       </c>
       <c r="M48">
-        <v>29.5317654</v>
+        <v>30.17376030000001</v>
       </c>
       <c r="N48">
-        <v>79.79323459999998</v>
+        <v>79.15123969999998</v>
       </c>
       <c r="O48">
-        <v>9.974154324999997</v>
+        <v>9.893904962499997</v>
       </c>
       <c r="P48">
-        <v>69.81908027499998</v>
+        <v>69.25733473749997</v>
       </c>
       <c r="Q48">
-        <v>84.11908027499999</v>
+        <v>83.55733473749999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1195868315909245</v>
+        <v>0.1208793290163198</v>
       </c>
       <c r="T48">
-        <v>1.438242687064536</v>
+        <v>1.463435867609683</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.701945973063973</v>
+        <v>3.623181165126441</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0892756693786495</v>
+        <v>0.08930119969819979</v>
       </c>
       <c r="C49">
-        <v>552.2166460836366</v>
+        <v>541.1910633401008</v>
       </c>
       <c r="D49">
-        <v>941.5476460836368</v>
+        <v>940.9950633401008</v>
       </c>
       <c r="E49">
-        <v>44.13100000000009</v>
+        <v>54.6040000000001</v>
       </c>
       <c r="F49">
-        <v>492.2310000000001</v>
+        <v>502.7040000000001</v>
       </c>
       <c r="G49">
         <v>102.9</v>
@@ -5311,28 +5311,28 @@
         <v>109.325</v>
       </c>
       <c r="M49">
-        <v>30.17376030000001</v>
+        <v>30.81575520000001</v>
       </c>
       <c r="N49">
-        <v>79.15123969999998</v>
+        <v>78.50924479999998</v>
       </c>
       <c r="O49">
-        <v>9.893904962499997</v>
+        <v>9.813655599999997</v>
       </c>
       <c r="P49">
-        <v>69.25733473749997</v>
+        <v>68.69558919999997</v>
       </c>
       <c r="Q49">
-        <v>83.55733473749999</v>
+        <v>82.99558919999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1208793290163198</v>
+        <v>0.1222215378811534</v>
       </c>
       <c r="T49">
-        <v>1.463435867609683</v>
+        <v>1.489598016637337</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.623181165126441</v>
+        <v>3.547698224186307</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08930119969819977</v>
+        <v>0.09052723001775004</v>
       </c>
       <c r="C50">
-        <v>541.1910633401011</v>
+        <v>504.9241906199651</v>
       </c>
       <c r="D50">
-        <v>940.9950633401012</v>
+        <v>915.2011906199652</v>
       </c>
       <c r="E50">
-        <v>54.60400000000004</v>
+        <v>65.07700000000011</v>
       </c>
       <c r="F50">
-        <v>502.7040000000001</v>
+        <v>513.1770000000001</v>
       </c>
       <c r="G50">
         <v>102.9</v>
@@ -5393,45 +5393,45 @@
         <v>109.325</v>
       </c>
       <c r="M50">
-        <v>30.81575520000001</v>
+        <v>32.89464570000001</v>
       </c>
       <c r="N50">
-        <v>78.50924479999998</v>
+        <v>76.43035429999998</v>
       </c>
       <c r="O50">
-        <v>9.813655599999997</v>
+        <v>9.553794287499997</v>
       </c>
       <c r="P50">
-        <v>68.69558919999997</v>
+        <v>66.87656001249998</v>
       </c>
       <c r="Q50">
-        <v>82.99558919999998</v>
+        <v>81.17656001249999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1222215378811534</v>
+        <v>0.1236163823877452</v>
       </c>
       <c r="T50">
-        <v>1.489598016637336</v>
+        <v>1.516786132293525</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.547698224186307</v>
+        <v>3.323489208458018</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09052723001775004</v>
+        <v>0.09057726033730032</v>
       </c>
       <c r="C51">
-        <v>504.9241906199651</v>
+        <v>493.4286222967895</v>
       </c>
       <c r="D51">
-        <v>915.2011906199652</v>
+        <v>914.1786222967896</v>
       </c>
       <c r="E51">
-        <v>65.07700000000011</v>
+        <v>75.55000000000007</v>
       </c>
       <c r="F51">
-        <v>513.1770000000001</v>
+        <v>523.6500000000001</v>
       </c>
       <c r="G51">
         <v>102.9</v>
@@ -5475,28 +5475,28 @@
         <v>109.325</v>
       </c>
       <c r="M51">
-        <v>32.89464570000001</v>
+        <v>33.56596500000001</v>
       </c>
       <c r="N51">
-        <v>76.43035429999998</v>
+        <v>75.75903499999998</v>
       </c>
       <c r="O51">
-        <v>9.553794287499997</v>
+        <v>9.469879374999998</v>
       </c>
       <c r="P51">
-        <v>66.87656001249998</v>
+        <v>66.28915562499998</v>
       </c>
       <c r="Q51">
-        <v>81.17656001249999</v>
+        <v>80.58915562499999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1236163823877452</v>
+        <v>0.1250670206746006</v>
       </c>
       <c r="T51">
-        <v>1.516786132293525</v>
+        <v>1.545061772575961</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.323489208458018</v>
+        <v>3.257019424288858</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09057726033730032</v>
+        <v>0.09062729065685057</v>
       </c>
       <c r="C52">
-        <v>493.4286222967895</v>
+        <v>481.9353364858617</v>
       </c>
       <c r="D52">
-        <v>914.1786222967896</v>
+        <v>913.1583364858618</v>
       </c>
       <c r="E52">
-        <v>75.55000000000007</v>
+        <v>86.02300000000002</v>
       </c>
       <c r="F52">
-        <v>523.6500000000001</v>
+        <v>534.123</v>
       </c>
       <c r="G52">
         <v>102.9</v>
@@ -5557,28 +5557,28 @@
         <v>109.325</v>
       </c>
       <c r="M52">
-        <v>33.56596500000001</v>
+        <v>34.23728430000001</v>
       </c>
       <c r="N52">
-        <v>75.75903499999998</v>
+        <v>75.08771569999999</v>
       </c>
       <c r="O52">
-        <v>9.469879374999998</v>
+        <v>9.385964462499999</v>
       </c>
       <c r="P52">
-        <v>66.28915562499998</v>
+        <v>65.70175123749999</v>
       </c>
       <c r="Q52">
-        <v>80.58915562499999</v>
+        <v>80.0017512375</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1250670206746006</v>
+        <v>0.1265768686874502</v>
       </c>
       <c r="T52">
-        <v>1.545061772575961</v>
+        <v>1.574491520625027</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.257019424288858</v>
+        <v>3.19315629832241</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09062729065685057</v>
+        <v>0.09067732097640085</v>
       </c>
       <c r="C53">
-        <v>481.9353364858617</v>
+        <v>470.4443255533816</v>
       </c>
       <c r="D53">
-        <v>913.1583364858618</v>
+        <v>912.1403255533818</v>
       </c>
       <c r="E53">
-        <v>86.02300000000002</v>
+        <v>96.49600000000009</v>
       </c>
       <c r="F53">
-        <v>534.123</v>
+        <v>544.5960000000001</v>
       </c>
       <c r="G53">
         <v>102.9</v>
@@ -5639,28 +5639,28 @@
         <v>109.325</v>
       </c>
       <c r="M53">
-        <v>34.23728430000001</v>
+        <v>34.90860360000001</v>
       </c>
       <c r="N53">
-        <v>75.08771569999999</v>
+        <v>74.41639639999998</v>
       </c>
       <c r="O53">
-        <v>9.385964462499999</v>
+        <v>9.302049549999998</v>
       </c>
       <c r="P53">
-        <v>65.70175123749999</v>
+        <v>65.11434684999999</v>
       </c>
       <c r="Q53">
-        <v>80.0017512375</v>
+        <v>79.41434685</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1265768686874502</v>
+        <v>0.1281496270341684</v>
       </c>
       <c r="T53">
-        <v>1.574491520625027</v>
+        <v>1.605147508176137</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.19315629832241</v>
+        <v>3.131749446431594</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09067732097640085</v>
+        <v>0.09072735129595112</v>
       </c>
       <c r="C54">
-        <v>470.4443255533816</v>
+        <v>458.9555818995545</v>
       </c>
       <c r="D54">
-        <v>912.1403255533818</v>
+        <v>911.1245818995546</v>
       </c>
       <c r="E54">
-        <v>96.49600000000009</v>
+        <v>106.9690000000001</v>
       </c>
       <c r="F54">
-        <v>544.5960000000001</v>
+        <v>555.0690000000001</v>
       </c>
       <c r="G54">
         <v>102.9</v>
@@ -5721,28 +5721,28 @@
         <v>109.325</v>
       </c>
       <c r="M54">
-        <v>34.90860360000001</v>
+        <v>35.57992290000001</v>
       </c>
       <c r="N54">
-        <v>74.41639639999998</v>
+        <v>73.74507709999997</v>
       </c>
       <c r="O54">
-        <v>9.302049549999998</v>
+        <v>9.218134637499997</v>
       </c>
       <c r="P54">
-        <v>65.11434684999999</v>
+        <v>64.52694246249997</v>
       </c>
       <c r="Q54">
-        <v>79.41434685</v>
+        <v>78.82694246249999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1281496270341684</v>
+        <v>0.1297893112679811</v>
       </c>
       <c r="T54">
-        <v>1.605147508176137</v>
+        <v>1.637108005835805</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.131749446431594</v>
+        <v>3.072659834234772</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09072735129595112</v>
+        <v>0.09077738161550138</v>
       </c>
       <c r="C55">
-        <v>458.9555818995545</v>
+        <v>447.4690979583992</v>
       </c>
       <c r="D55">
-        <v>911.1245818995546</v>
+        <v>910.1110979583993</v>
       </c>
       <c r="E55">
-        <v>106.9690000000001</v>
+        <v>117.4420000000001</v>
       </c>
       <c r="F55">
-        <v>555.0690000000001</v>
+        <v>565.5420000000001</v>
       </c>
       <c r="G55">
         <v>102.9</v>
@@ -5803,28 +5803,28 @@
         <v>109.325</v>
       </c>
       <c r="M55">
-        <v>35.57992290000001</v>
+        <v>36.25124220000001</v>
       </c>
       <c r="N55">
-        <v>73.74507709999997</v>
+        <v>73.07375779999998</v>
       </c>
       <c r="O55">
-        <v>9.218134637499997</v>
+        <v>9.134219724999998</v>
       </c>
       <c r="P55">
-        <v>64.52694246249997</v>
+        <v>63.93953807499999</v>
       </c>
       <c r="Q55">
-        <v>78.82694246249999</v>
+        <v>78.239538075</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1297893112679811</v>
+        <v>0.1315002861206552</v>
       </c>
       <c r="T55">
-        <v>1.637108005835805</v>
+        <v>1.670458090350242</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.072659834234772</v>
+        <v>3.015758726193387</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09077738161550138</v>
+        <v>0.09458116193505164</v>
       </c>
       <c r="C56">
-        <v>447.4690979583992</v>
+        <v>366.0288936997624</v>
       </c>
       <c r="D56">
-        <v>910.1110979583993</v>
+        <v>839.1438936997625</v>
       </c>
       <c r="E56">
-        <v>117.4420000000001</v>
+        <v>127.9150000000001</v>
       </c>
       <c r="F56">
-        <v>565.5420000000001</v>
+        <v>576.0150000000001</v>
       </c>
       <c r="G56">
         <v>102.9</v>
@@ -5885,45 +5885,45 @@
         <v>109.325</v>
       </c>
       <c r="M56">
-        <v>36.25124220000001</v>
+        <v>41.41547850000001</v>
       </c>
       <c r="N56">
-        <v>73.07375779999998</v>
+        <v>67.90952149999998</v>
       </c>
       <c r="O56">
-        <v>9.134219724999998</v>
+        <v>8.488690187499998</v>
       </c>
       <c r="P56">
-        <v>63.93953807499999</v>
+        <v>59.42083131249998</v>
       </c>
       <c r="Q56">
-        <v>78.239538075</v>
+        <v>73.7208313125</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1315002861206552</v>
+        <v>0.1332873043001148</v>
       </c>
       <c r="T56">
-        <v>1.670458090350242</v>
+        <v>1.705290400843098</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.125</v>
       </c>
       <c r="W56">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.015758726193387</v>
+        <v>2.63971355540417</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09458116193505164</v>
+        <v>0.09469944225460192</v>
       </c>
       <c r="C57">
-        <v>366.0288936997624</v>
+        <v>353.5261321458639</v>
       </c>
       <c r="D57">
-        <v>839.1438936997625</v>
+        <v>837.1141321458641</v>
       </c>
       <c r="E57">
-        <v>127.9150000000001</v>
+        <v>138.3880000000001</v>
       </c>
       <c r="F57">
-        <v>576.0150000000001</v>
+        <v>586.4880000000002</v>
       </c>
       <c r="G57">
         <v>102.9</v>
@@ -5967,28 +5967,28 @@
         <v>109.325</v>
       </c>
       <c r="M57">
-        <v>41.41547850000001</v>
+        <v>42.16848720000002</v>
       </c>
       <c r="N57">
-        <v>67.90952149999998</v>
+        <v>67.15651279999997</v>
       </c>
       <c r="O57">
-        <v>8.488690187499998</v>
+        <v>8.394564099999997</v>
       </c>
       <c r="P57">
-        <v>59.42083131249998</v>
+        <v>58.76194869999998</v>
       </c>
       <c r="Q57">
-        <v>73.7208313125</v>
+        <v>73.06194869999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1332873043001148</v>
+        <v>0.1351555505786407</v>
       </c>
       <c r="T57">
-        <v>1.705290400843098</v>
+        <v>1.741705998176538</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.63971355540417</v>
+        <v>2.592575813343381</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09469944225460192</v>
+        <v>0.09481772257415218</v>
       </c>
       <c r="C58">
-        <v>353.5261321458639</v>
+        <v>341.0331662671869</v>
       </c>
       <c r="D58">
-        <v>837.1141321458641</v>
+        <v>835.094166267187</v>
       </c>
       <c r="E58">
-        <v>138.3880000000001</v>
+        <v>148.8610000000001</v>
       </c>
       <c r="F58">
-        <v>586.4880000000002</v>
+        <v>596.9610000000001</v>
       </c>
       <c r="G58">
         <v>102.9</v>
@@ -6049,28 +6049,28 @@
         <v>109.325</v>
       </c>
       <c r="M58">
-        <v>42.16848720000002</v>
+        <v>42.92149590000001</v>
       </c>
       <c r="N58">
-        <v>67.15651279999997</v>
+        <v>66.40350409999998</v>
       </c>
       <c r="O58">
-        <v>8.394564099999997</v>
+        <v>8.300438012499997</v>
       </c>
       <c r="P58">
-        <v>58.76194869999998</v>
+        <v>58.10306608749998</v>
       </c>
       <c r="Q58">
-        <v>73.06194869999999</v>
+        <v>72.40306608749999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1351555505786407</v>
+        <v>0.137110692032912</v>
       </c>
       <c r="T58">
-        <v>1.741705998176538</v>
+        <v>1.779815344223161</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.592575813343381</v>
+        <v>2.547092027144375</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09481772257415218</v>
+        <v>0.09493600289370245</v>
       </c>
       <c r="C59">
-        <v>341.0331662671869</v>
+        <v>328.5499253232025</v>
       </c>
       <c r="D59">
-        <v>835.094166267187</v>
+        <v>833.0839253232027</v>
       </c>
       <c r="E59">
-        <v>148.8610000000001</v>
+        <v>159.3340000000002</v>
       </c>
       <c r="F59">
-        <v>596.9610000000001</v>
+        <v>607.4340000000002</v>
       </c>
       <c r="G59">
         <v>102.9</v>
@@ -6131,28 +6131,28 @@
         <v>109.325</v>
       </c>
       <c r="M59">
-        <v>42.92149590000001</v>
+        <v>43.67450460000002</v>
       </c>
       <c r="N59">
-        <v>66.40350409999998</v>
+        <v>65.65049539999997</v>
       </c>
       <c r="O59">
-        <v>8.300438012499997</v>
+        <v>8.206311924999996</v>
       </c>
       <c r="P59">
-        <v>58.10306608749998</v>
+        <v>57.44418347499997</v>
       </c>
       <c r="Q59">
-        <v>72.40306608749999</v>
+        <v>71.74418347499999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.137110692032912</v>
+        <v>0.1391589354611963</v>
       </c>
       <c r="T59">
-        <v>1.779815344223161</v>
+        <v>1.81973942103391</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.547092027144375</v>
+        <v>2.503176647366023</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09493600289370244</v>
+        <v>0.09706765821325271</v>
       </c>
       <c r="C60">
-        <v>328.5499253232028</v>
+        <v>283.4381717124915</v>
       </c>
       <c r="D60">
-        <v>833.0839253232029</v>
+        <v>798.4451717124915</v>
       </c>
       <c r="E60">
-        <v>159.3340000000001</v>
+        <v>169.807</v>
       </c>
       <c r="F60">
-        <v>607.4340000000001</v>
+        <v>617.907</v>
       </c>
       <c r="G60">
         <v>102.9</v>
@@ -6213,45 +6213,45 @@
         <v>109.325</v>
       </c>
       <c r="M60">
-        <v>43.67450460000001</v>
+        <v>46.83735060000001</v>
       </c>
       <c r="N60">
-        <v>65.65049539999998</v>
+        <v>62.48764939999998</v>
       </c>
       <c r="O60">
-        <v>8.206311924999998</v>
+        <v>7.810956174999998</v>
       </c>
       <c r="P60">
-        <v>57.44418347499999</v>
+        <v>54.67669322499998</v>
       </c>
       <c r="Q60">
-        <v>71.744183475</v>
+        <v>68.97669322499999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1391589354611963</v>
+        <v>0.1413070932030554</v>
       </c>
       <c r="T60">
-        <v>1.819739421033909</v>
+        <v>1.861611013786645</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.125</v>
       </c>
       <c r="W60">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.503176647366024</v>
+        <v>2.33414141917754</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09706765821325271</v>
+        <v>0.09722006353280296</v>
       </c>
       <c r="C61">
-        <v>283.4381717124915</v>
+        <v>270.5986384338896</v>
       </c>
       <c r="D61">
-        <v>798.4451717124915</v>
+        <v>796.0786384338898</v>
       </c>
       <c r="E61">
-        <v>169.807</v>
+        <v>180.2800000000001</v>
       </c>
       <c r="F61">
-        <v>617.907</v>
+        <v>628.3800000000001</v>
       </c>
       <c r="G61">
         <v>102.9</v>
@@ -6295,28 +6295,28 @@
         <v>109.325</v>
       </c>
       <c r="M61">
-        <v>46.83735060000001</v>
+        <v>47.63120400000001</v>
       </c>
       <c r="N61">
-        <v>62.48764939999998</v>
+        <v>61.69379599999998</v>
       </c>
       <c r="O61">
-        <v>7.810956174999998</v>
+        <v>7.711724499999997</v>
       </c>
       <c r="P61">
-        <v>54.67669322499998</v>
+        <v>53.98207149999998</v>
       </c>
       <c r="Q61">
-        <v>68.97669322499999</v>
+        <v>68.2820715</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1413070932030554</v>
+        <v>0.1435626588320074</v>
       </c>
       <c r="T61">
-        <v>1.861611013786645</v>
+        <v>1.905576186177018</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.33414141917754</v>
+        <v>2.295239062191247</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09722006353280296</v>
+        <v>0.09737246885235323</v>
       </c>
       <c r="C62">
-        <v>270.5986384338896</v>
+        <v>257.7730921630293</v>
       </c>
       <c r="D62">
-        <v>796.0786384338898</v>
+        <v>793.7260921630294</v>
       </c>
       <c r="E62">
-        <v>180.2800000000001</v>
+        <v>190.753</v>
       </c>
       <c r="F62">
-        <v>628.3800000000001</v>
+        <v>638.8530000000001</v>
       </c>
       <c r="G62">
         <v>102.9</v>
@@ -6377,28 +6377,28 @@
         <v>109.325</v>
       </c>
       <c r="M62">
-        <v>47.63120400000001</v>
+        <v>48.42505740000001</v>
       </c>
       <c r="N62">
-        <v>61.69379599999998</v>
+        <v>60.89994259999998</v>
       </c>
       <c r="O62">
-        <v>7.711724499999997</v>
+        <v>7.612492824999998</v>
       </c>
       <c r="P62">
-        <v>53.98207149999998</v>
+        <v>53.28744977499998</v>
       </c>
       <c r="Q62">
-        <v>68.2820715</v>
+        <v>67.587449775</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1435626588320074</v>
+        <v>0.1459338944932134</v>
       </c>
       <c r="T62">
-        <v>1.905576186177018</v>
+        <v>1.951795982792538</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.295239062191247</v>
+        <v>2.257612192319259</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09737246885235323</v>
+        <v>0.0975248741719035</v>
       </c>
       <c r="C63">
-        <v>257.7730921630293</v>
+        <v>244.9614092633964</v>
       </c>
       <c r="D63">
-        <v>793.7260921630294</v>
+        <v>791.3874092633965</v>
       </c>
       <c r="E63">
-        <v>190.753</v>
+        <v>201.2260000000001</v>
       </c>
       <c r="F63">
-        <v>638.8530000000001</v>
+        <v>649.3260000000001</v>
       </c>
       <c r="G63">
         <v>102.9</v>
@@ -6459,28 +6459,28 @@
         <v>109.325</v>
       </c>
       <c r="M63">
-        <v>48.42505740000001</v>
+        <v>49.21891080000002</v>
       </c>
       <c r="N63">
-        <v>60.89994259999998</v>
+        <v>60.10608919999997</v>
       </c>
       <c r="O63">
-        <v>7.612492824999998</v>
+        <v>7.513261149999996</v>
       </c>
       <c r="P63">
-        <v>53.28744977499998</v>
+        <v>52.59282804999997</v>
       </c>
       <c r="Q63">
-        <v>67.587449775</v>
+        <v>66.89282804999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1459338944932134</v>
+        <v>0.148429932031325</v>
       </c>
       <c r="T63">
-        <v>1.951795982792538</v>
+        <v>2.00044840028256</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.257612192319259</v>
+        <v>2.221199092443142</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0975248741719035</v>
+        <v>0.09767727949145377</v>
       </c>
       <c r="C64">
-        <v>244.9614092633964</v>
+        <v>232.1634675513562</v>
       </c>
       <c r="D64">
-        <v>791.3874092633965</v>
+        <v>789.0624675513563</v>
       </c>
       <c r="E64">
-        <v>201.2260000000001</v>
+        <v>211.6990000000001</v>
       </c>
       <c r="F64">
-        <v>649.3260000000001</v>
+        <v>659.7990000000001</v>
       </c>
       <c r="G64">
         <v>102.9</v>
@@ -6541,28 +6541,28 @@
         <v>109.325</v>
       </c>
       <c r="M64">
-        <v>49.21891080000002</v>
+        <v>50.01276420000001</v>
       </c>
       <c r="N64">
-        <v>60.10608919999997</v>
+        <v>59.31223579999997</v>
       </c>
       <c r="O64">
-        <v>7.513261149999996</v>
+        <v>7.414029474999997</v>
       </c>
       <c r="P64">
-        <v>52.59282804999997</v>
+        <v>51.89820632499998</v>
       </c>
       <c r="Q64">
-        <v>66.89282804999999</v>
+        <v>66.19820632499999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.148429932031325</v>
+        <v>0.1510608905174426</v>
       </c>
       <c r="T64">
-        <v>2.00044840028256</v>
+        <v>2.051730678177447</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.221199092443142</v>
+        <v>2.185941963991664</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09767727949145377</v>
+        <v>0.09782968481100403</v>
       </c>
       <c r="C65">
-        <v>232.1634675513562</v>
+        <v>219.3791462748751</v>
       </c>
       <c r="D65">
-        <v>789.0624675513563</v>
+        <v>786.7511462748753</v>
       </c>
       <c r="E65">
-        <v>211.6990000000001</v>
+        <v>222.1720000000001</v>
       </c>
       <c r="F65">
-        <v>659.7990000000001</v>
+        <v>670.2720000000002</v>
       </c>
       <c r="G65">
         <v>102.9</v>
@@ -6623,28 +6623,28 @@
         <v>109.325</v>
       </c>
       <c r="M65">
-        <v>50.01276420000001</v>
+        <v>50.80661760000002</v>
       </c>
       <c r="N65">
-        <v>59.31223579999997</v>
+        <v>58.51838239999997</v>
       </c>
       <c r="O65">
-        <v>7.414029474999997</v>
+        <v>7.314797799999996</v>
       </c>
       <c r="P65">
-        <v>51.89820632499998</v>
+        <v>51.20358459999998</v>
       </c>
       <c r="Q65">
-        <v>66.19820632499999</v>
+        <v>65.50358459999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1510608905174426</v>
+        <v>0.1538380133639001</v>
       </c>
       <c r="T65">
-        <v>2.051730678177447</v>
+        <v>2.105861971510939</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.185941963991664</v>
+        <v>2.151786620804294</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09782968481100403</v>
+        <v>0.09798209013055431</v>
       </c>
       <c r="C66">
-        <v>219.3791462748751</v>
+        <v>206.6083260926137</v>
       </c>
       <c r="D66">
-        <v>786.7511462748753</v>
+        <v>784.4533260926138</v>
       </c>
       <c r="E66">
-        <v>222.1720000000001</v>
+        <v>232.6450000000001</v>
       </c>
       <c r="F66">
-        <v>670.2720000000002</v>
+        <v>680.7450000000001</v>
       </c>
       <c r="G66">
         <v>102.9</v>
@@ -6705,28 +6705,28 @@
         <v>109.325</v>
       </c>
       <c r="M66">
-        <v>50.80661760000002</v>
+        <v>51.60047100000001</v>
       </c>
       <c r="N66">
-        <v>58.51838239999997</v>
+        <v>57.72452899999998</v>
       </c>
       <c r="O66">
-        <v>7.314797799999996</v>
+        <v>7.215566124999997</v>
       </c>
       <c r="P66">
-        <v>51.20358459999998</v>
+        <v>50.50896287499998</v>
       </c>
       <c r="Q66">
-        <v>65.50358459999998</v>
+        <v>64.80896287499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1538380133639001</v>
+        <v>0.1567738289444409</v>
       </c>
       <c r="T66">
-        <v>2.105861971510939</v>
+        <v>2.163086481606345</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.151786620804294</v>
+        <v>2.118682211253458</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09798209013055431</v>
+        <v>0.09813449545010458</v>
       </c>
       <c r="C67">
-        <v>206.6083260926137</v>
+        <v>193.8508890533877</v>
       </c>
       <c r="D67">
-        <v>784.4533260926138</v>
+        <v>782.1688890533879</v>
       </c>
       <c r="E67">
-        <v>232.6450000000001</v>
+        <v>243.1180000000002</v>
       </c>
       <c r="F67">
-        <v>680.7450000000001</v>
+        <v>691.2180000000002</v>
       </c>
       <c r="G67">
         <v>102.9</v>
@@ -6787,28 +6787,28 @@
         <v>109.325</v>
       </c>
       <c r="M67">
-        <v>51.60047100000001</v>
+        <v>52.39432440000002</v>
       </c>
       <c r="N67">
-        <v>57.72452899999998</v>
+        <v>56.93067559999997</v>
       </c>
       <c r="O67">
-        <v>7.215566124999997</v>
+        <v>7.116334449999997</v>
       </c>
       <c r="P67">
-        <v>50.50896287499998</v>
+        <v>49.81434114999998</v>
       </c>
       <c r="Q67">
-        <v>64.80896287499999</v>
+        <v>64.11434114999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1567738289444409</v>
+        <v>0.1598823395591311</v>
       </c>
       <c r="T67">
-        <v>2.163086481606345</v>
+        <v>2.223677139354422</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.118682211253458</v>
+        <v>2.086580965628406</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09813449545010458</v>
+        <v>0.09828690076965485</v>
       </c>
       <c r="C68">
-        <v>193.8508890533877</v>
+        <v>181.106718575984</v>
       </c>
       <c r="D68">
-        <v>782.1688890533879</v>
+        <v>779.8977185759842</v>
       </c>
       <c r="E68">
-        <v>243.1180000000002</v>
+        <v>253.5910000000001</v>
       </c>
       <c r="F68">
-        <v>691.2180000000002</v>
+        <v>701.6910000000001</v>
       </c>
       <c r="G68">
         <v>102.9</v>
@@ -6869,28 +6869,28 @@
         <v>109.325</v>
       </c>
       <c r="M68">
-        <v>52.39432440000002</v>
+        <v>53.18817780000001</v>
       </c>
       <c r="N68">
-        <v>56.93067559999997</v>
+        <v>56.13682219999998</v>
       </c>
       <c r="O68">
-        <v>7.116334449999997</v>
+        <v>7.017102774999997</v>
       </c>
       <c r="P68">
-        <v>49.81434114999998</v>
+        <v>49.11971942499998</v>
       </c>
       <c r="Q68">
-        <v>64.11434114999999</v>
+        <v>63.41971942499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1598823395591311</v>
+        <v>0.1631792447565298</v>
       </c>
       <c r="T68">
-        <v>2.223677139354422</v>
+        <v>2.28793995817814</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.086580965628406</v>
+        <v>2.055437966141415</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09828690076965485</v>
+        <v>0.09843930608920512</v>
       </c>
       <c r="C69">
-        <v>181.106718575984</v>
+        <v>168.3756994293282</v>
       </c>
       <c r="D69">
-        <v>779.8977185759842</v>
+        <v>777.6396994293284</v>
       </c>
       <c r="E69">
-        <v>253.5910000000001</v>
+        <v>264.0640000000002</v>
       </c>
       <c r="F69">
-        <v>701.6910000000001</v>
+        <v>712.1640000000002</v>
       </c>
       <c r="G69">
         <v>102.9</v>
@@ -6951,28 +6951,28 @@
         <v>109.325</v>
       </c>
       <c r="M69">
-        <v>53.18817780000001</v>
+        <v>53.98203120000002</v>
       </c>
       <c r="N69">
-        <v>56.13682219999998</v>
+        <v>55.34296879999997</v>
       </c>
       <c r="O69">
-        <v>7.017102774999997</v>
+        <v>6.917871099999996</v>
       </c>
       <c r="P69">
-        <v>49.11971942499998</v>
+        <v>48.42509769999997</v>
       </c>
       <c r="Q69">
-        <v>63.41971942499999</v>
+        <v>62.72509769999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1631792447565298</v>
+        <v>0.166682206528766</v>
       </c>
       <c r="T69">
-        <v>2.28793995817814</v>
+        <v>2.356219203178341</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.055437966141415</v>
+        <v>2.025210937227571</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09843930608920512</v>
+        <v>0.1071649614087554</v>
       </c>
       <c r="C70">
-        <v>168.3756994293282</v>
+        <v>47.32793780239672</v>
       </c>
       <c r="D70">
-        <v>777.6396994293284</v>
+        <v>667.0649378023969</v>
       </c>
       <c r="E70">
-        <v>264.0640000000002</v>
+        <v>274.5370000000001</v>
       </c>
       <c r="F70">
-        <v>712.1640000000002</v>
+        <v>722.6370000000002</v>
       </c>
       <c r="G70">
         <v>102.9</v>
@@ -7033,45 +7033,45 @@
         <v>109.325</v>
       </c>
       <c r="M70">
-        <v>53.98203120000002</v>
+        <v>65.03733000000001</v>
       </c>
       <c r="N70">
-        <v>55.34296879999997</v>
+        <v>44.28766999999998</v>
       </c>
       <c r="O70">
-        <v>6.917871099999996</v>
+        <v>5.535958749999997</v>
       </c>
       <c r="P70">
-        <v>48.42509769999997</v>
+        <v>38.75171124999998</v>
       </c>
       <c r="Q70">
-        <v>62.72509769999998</v>
+        <v>53.05171124999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.166682206528766</v>
+        <v>0.1704111658346948</v>
       </c>
       <c r="T70">
-        <v>2.356219203178341</v>
+        <v>2.428903560759199</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
         <v>0.125</v>
       </c>
       <c r="W70">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.025210937227571</v>
+        <v>1.680957689991271</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1071649614087554</v>
+        <v>0.1074416167283056</v>
       </c>
       <c r="C71">
-        <v>47.32793780239672</v>
+        <v>33.8610665620962</v>
       </c>
       <c r="D71">
-        <v>667.0649378023969</v>
+        <v>664.0710665620965</v>
       </c>
       <c r="E71">
-        <v>274.5370000000001</v>
+        <v>285.0100000000002</v>
       </c>
       <c r="F71">
-        <v>722.6370000000002</v>
+        <v>733.1100000000002</v>
       </c>
       <c r="G71">
         <v>102.9</v>
@@ -7115,28 +7115,28 @@
         <v>109.325</v>
       </c>
       <c r="M71">
-        <v>65.03733000000001</v>
+        <v>65.97990000000001</v>
       </c>
       <c r="N71">
-        <v>44.28766999999998</v>
+        <v>43.34509999999997</v>
       </c>
       <c r="O71">
-        <v>5.535958749999997</v>
+        <v>5.418137499999997</v>
       </c>
       <c r="P71">
-        <v>38.75171124999998</v>
+        <v>37.92696249999997</v>
       </c>
       <c r="Q71">
-        <v>53.05171124999999</v>
+        <v>52.22696249999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1704111658346948</v>
+        <v>0.1743887224276855</v>
       </c>
       <c r="T71">
-        <v>2.428903560759199</v>
+        <v>2.506433542178781</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.680957689991271</v>
+        <v>1.656944008705681</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1074416167283056</v>
+        <v>0.1077182720478559</v>
       </c>
       <c r="C72">
-        <v>33.8610665620962</v>
+        <v>20.42094898843663</v>
       </c>
       <c r="D72">
-        <v>664.0710665620965</v>
+        <v>661.1039489884369</v>
       </c>
       <c r="E72">
-        <v>285.0100000000002</v>
+        <v>295.4830000000002</v>
       </c>
       <c r="F72">
-        <v>733.1100000000002</v>
+        <v>743.5830000000002</v>
       </c>
       <c r="G72">
         <v>102.9</v>
@@ -7197,28 +7197,28 @@
         <v>109.325</v>
       </c>
       <c r="M72">
-        <v>65.97990000000001</v>
+        <v>66.92247000000002</v>
       </c>
       <c r="N72">
-        <v>43.34509999999997</v>
+        <v>42.40252999999997</v>
       </c>
       <c r="O72">
-        <v>5.418137499999997</v>
+        <v>5.300316249999996</v>
       </c>
       <c r="P72">
-        <v>37.92696249999997</v>
+        <v>37.10221374999998</v>
       </c>
       <c r="Q72">
-        <v>52.22696249999998</v>
+        <v>51.40221374999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1743887224276855</v>
+        <v>0.1786405932684687</v>
       </c>
       <c r="T72">
-        <v>2.506433542178781</v>
+        <v>2.58931041886868</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.656944008705681</v>
+        <v>1.633606769146446</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1077182720478559</v>
+        <v>0.1079949273674062</v>
       </c>
       <c r="C73">
-        <v>20.42094898843675</v>
+        <v>7.007228064640003</v>
       </c>
       <c r="D73">
-        <v>661.1039489884369</v>
+        <v>658.1632280646402</v>
       </c>
       <c r="E73">
-        <v>295.4830000000001</v>
+        <v>305.9560000000001</v>
       </c>
       <c r="F73">
-        <v>743.5830000000001</v>
+        <v>754.0560000000002</v>
       </c>
       <c r="G73">
         <v>102.9</v>
@@ -7279,28 +7279,28 @@
         <v>109.325</v>
       </c>
       <c r="M73">
-        <v>66.92247</v>
+        <v>67.86504000000001</v>
       </c>
       <c r="N73">
-        <v>42.40252999999998</v>
+        <v>41.45995999999998</v>
       </c>
       <c r="O73">
-        <v>5.300316249999998</v>
+        <v>5.182494999999998</v>
       </c>
       <c r="P73">
-        <v>37.10221374999999</v>
+        <v>36.27746499999999</v>
       </c>
       <c r="Q73">
-        <v>51.40221375</v>
+        <v>50.577465</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1786405932684686</v>
+        <v>0.1831961691693078</v>
       </c>
       <c r="T73">
-        <v>2.589310418868679</v>
+        <v>2.678107072464999</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.633606769146446</v>
+        <v>1.610917786241635</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1079949273674062</v>
+        <v>0.1082715826869564</v>
       </c>
       <c r="C74">
-        <v>7.007228064640003</v>
+        <v>-6.380446901878372</v>
       </c>
       <c r="D74">
-        <v>658.1632280646402</v>
+        <v>655.2485530981218</v>
       </c>
       <c r="E74">
-        <v>305.9560000000001</v>
+        <v>316.4290000000001</v>
       </c>
       <c r="F74">
-        <v>754.0560000000002</v>
+        <v>764.5290000000001</v>
       </c>
       <c r="G74">
         <v>102.9</v>
@@ -7361,28 +7361,28 @@
         <v>109.325</v>
       </c>
       <c r="M74">
-        <v>67.86504000000001</v>
+        <v>68.80761000000001</v>
       </c>
       <c r="N74">
-        <v>41.45995999999998</v>
+        <v>40.51738999999998</v>
       </c>
       <c r="O74">
-        <v>5.182494999999998</v>
+        <v>5.064673749999997</v>
       </c>
       <c r="P74">
-        <v>36.27746499999999</v>
+        <v>35.45271624999998</v>
       </c>
       <c r="Q74">
-        <v>50.577465</v>
+        <v>49.75271624999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1831961691693078</v>
+        <v>0.1880891951368757</v>
       </c>
       <c r="T74">
-        <v>2.678107072464999</v>
+        <v>2.773481255957342</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.610917786241635</v>
+        <v>1.588850419306818</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1082715826869564</v>
+        <v>0.1085482380065067</v>
       </c>
       <c r="C75">
-        <v>-6.380446901878372</v>
+        <v>-19.74242041892614</v>
       </c>
       <c r="D75">
-        <v>655.2485530981218</v>
+        <v>652.3595795810741</v>
       </c>
       <c r="E75">
-        <v>316.4290000000001</v>
+        <v>326.9020000000002</v>
       </c>
       <c r="F75">
-        <v>764.5290000000001</v>
+        <v>775.0020000000002</v>
       </c>
       <c r="G75">
         <v>102.9</v>
@@ -7443,28 +7443,28 @@
         <v>109.325</v>
       </c>
       <c r="M75">
-        <v>68.80761000000001</v>
+        <v>69.75018000000001</v>
       </c>
       <c r="N75">
-        <v>40.51738999999998</v>
+        <v>39.57481999999997</v>
       </c>
       <c r="O75">
-        <v>5.064673749999997</v>
+        <v>4.946852499999997</v>
       </c>
       <c r="P75">
-        <v>35.45271624999998</v>
+        <v>34.62796749999998</v>
       </c>
       <c r="Q75">
-        <v>49.75271624999999</v>
+        <v>48.92796749999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1880891951368757</v>
+        <v>0.1933586077173335</v>
       </c>
       <c r="T75">
-        <v>2.773481255957342</v>
+        <v>2.876191915102942</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.588850419306818</v>
+        <v>1.567379467694563</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1085482380065067</v>
+        <v>0.108824893326057</v>
       </c>
       <c r="C76">
-        <v>-19.74242041892614</v>
+        <v>-33.07903094527774</v>
       </c>
       <c r="D76">
-        <v>652.3595795810741</v>
+        <v>649.4959690547224</v>
       </c>
       <c r="E76">
-        <v>326.9020000000002</v>
+        <v>337.3750000000001</v>
       </c>
       <c r="F76">
-        <v>775.0020000000002</v>
+        <v>785.4750000000001</v>
       </c>
       <c r="G76">
         <v>102.9</v>
@@ -7525,28 +7525,28 @@
         <v>109.325</v>
       </c>
       <c r="M76">
-        <v>69.75018000000001</v>
+        <v>70.69275</v>
       </c>
       <c r="N76">
-        <v>39.57481999999997</v>
+        <v>38.63224999999998</v>
       </c>
       <c r="O76">
-        <v>4.946852499999997</v>
+        <v>4.829031249999998</v>
       </c>
       <c r="P76">
-        <v>34.62796749999998</v>
+        <v>33.80321874999998</v>
       </c>
       <c r="Q76">
-        <v>48.92796749999999</v>
+        <v>48.10321875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1933586077173335</v>
+        <v>0.1990495733042279</v>
       </c>
       <c r="T76">
-        <v>2.876191915102942</v>
+        <v>2.987119426980191</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.567379467694563</v>
+        <v>1.546481074791969</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.108824893326057</v>
+        <v>0.1091015486456072</v>
       </c>
       <c r="C77">
-        <v>-33.07903094527774</v>
+        <v>-46.39061102285848</v>
       </c>
       <c r="D77">
-        <v>649.4959690547224</v>
+        <v>646.6573889771416</v>
       </c>
       <c r="E77">
-        <v>337.3750000000001</v>
+        <v>347.8480000000001</v>
       </c>
       <c r="F77">
-        <v>785.4750000000001</v>
+        <v>795.9480000000001</v>
       </c>
       <c r="G77">
         <v>102.9</v>
@@ -7607,28 +7607,28 @@
         <v>109.325</v>
       </c>
       <c r="M77">
-        <v>70.69275</v>
+        <v>71.63532000000001</v>
       </c>
       <c r="N77">
-        <v>38.63224999999998</v>
+        <v>37.68967999999998</v>
       </c>
       <c r="O77">
-        <v>4.829031249999998</v>
+        <v>4.711209999999998</v>
       </c>
       <c r="P77">
-        <v>33.80321874999998</v>
+        <v>32.97846999999999</v>
       </c>
       <c r="Q77">
-        <v>48.10321875</v>
+        <v>47.27847</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1990495733042279</v>
+        <v>0.2052147860233635</v>
       </c>
       <c r="T77">
-        <v>2.987119426980191</v>
+        <v>3.107290898180544</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.546481074791969</v>
+        <v>1.526132639597338</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1091015486456072</v>
+        <v>0.1093782039651575</v>
       </c>
       <c r="C78">
-        <v>-46.39061102285848</v>
+        <v>-59.6774874054795</v>
       </c>
       <c r="D78">
-        <v>646.6573889771416</v>
+        <v>643.8435125945207</v>
       </c>
       <c r="E78">
-        <v>347.8480000000001</v>
+        <v>358.3210000000001</v>
       </c>
       <c r="F78">
-        <v>795.9480000000001</v>
+        <v>806.4210000000002</v>
       </c>
       <c r="G78">
         <v>102.9</v>
@@ -7689,28 +7689,28 @@
         <v>109.325</v>
       </c>
       <c r="M78">
-        <v>71.63532000000001</v>
+        <v>72.57789000000001</v>
       </c>
       <c r="N78">
-        <v>37.68967999999998</v>
+        <v>36.74710999999998</v>
       </c>
       <c r="O78">
-        <v>4.711209999999998</v>
+        <v>4.593388749999997</v>
       </c>
       <c r="P78">
-        <v>32.97846999999999</v>
+        <v>32.15372124999998</v>
       </c>
       <c r="Q78">
-        <v>47.27847</v>
+        <v>46.45372124999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2052147860233635</v>
+        <v>0.2119161041963369</v>
       </c>
       <c r="T78">
-        <v>3.107290898180544</v>
+        <v>3.237912062528753</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.526132639597338</v>
+        <v>1.506312735186983</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1093782039651575</v>
+        <v>0.1500495973281653</v>
       </c>
       <c r="C79">
-        <v>-59.6774874054795</v>
+        <v>-321.3362323491456</v>
       </c>
       <c r="D79">
-        <v>643.8435125945207</v>
+        <v>392.6577676508546</v>
       </c>
       <c r="E79">
-        <v>358.3210000000001</v>
+        <v>368.7940000000001</v>
       </c>
       <c r="F79">
-        <v>806.4210000000002</v>
+        <v>816.8940000000001</v>
       </c>
       <c r="G79">
         <v>102.9</v>
@@ -7771,45 +7771,45 @@
         <v>109.325</v>
       </c>
       <c r="M79">
-        <v>72.57789000000001</v>
+        <v>119.9200392</v>
       </c>
       <c r="N79">
-        <v>36.74710999999998</v>
+        <v>-10.59503920000004</v>
       </c>
       <c r="O79">
-        <v>4.593388749999997</v>
+        <v>-1.324379900000006</v>
       </c>
       <c r="P79">
-        <v>32.15372124999998</v>
+        <v>-9.270659300000039</v>
       </c>
       <c r="Q79">
-        <v>46.45372124999999</v>
+        <v>5.029340699999972</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2119161041963369</v>
+        <v>0.2208819608941934</v>
       </c>
       <c r="T79">
-        <v>3.237912062528753</v>
+        <v>3.412673297710271</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.125</v>
+        <v>0.1139561418689062</v>
       </c>
       <c r="W79">
-        <v>0.07875</v>
+        <v>0.1300712383736446</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.506312735186983</v>
+        <v>0.9116491349512498</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1500495973281653</v>
+        <v>0.1510595973281653</v>
       </c>
       <c r="C80">
-        <v>-321.3362323491456</v>
+        <v>-335.5769110729293</v>
       </c>
       <c r="D80">
-        <v>392.6577676508546</v>
+        <v>388.8900889270708</v>
       </c>
       <c r="E80">
-        <v>368.7940000000001</v>
+        <v>379.2670000000002</v>
       </c>
       <c r="F80">
-        <v>816.8940000000001</v>
+        <v>827.3670000000002</v>
       </c>
       <c r="G80">
         <v>102.9</v>
@@ -7853,37 +7853,37 @@
         <v>109.325</v>
       </c>
       <c r="M80">
-        <v>119.9200392</v>
+        <v>121.4574756</v>
       </c>
       <c r="N80">
-        <v>-10.59503920000004</v>
+        <v>-12.13247560000005</v>
       </c>
       <c r="O80">
-        <v>-1.324379900000006</v>
+        <v>-1.516559450000006</v>
       </c>
       <c r="P80">
-        <v>-9.270659300000039</v>
+        <v>-10.61591615000004</v>
       </c>
       <c r="Q80">
-        <v>5.029340699999972</v>
+        <v>3.684083849999968</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2208819608941934</v>
+        <v>0.2292191971272503</v>
       </c>
       <c r="T80">
-        <v>3.412673297710271</v>
+        <v>3.575181549982189</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1139561418689062</v>
+        <v>0.112513659060439</v>
       </c>
       <c r="W80">
-        <v>0.1300712383736446</v>
+        <v>0.1302829948499276</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9116491349512498</v>
+        <v>0.9001092724835124</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1510595973281653</v>
+        <v>0.1520695973281653</v>
       </c>
       <c r="C81">
-        <v>-335.5769110729293</v>
+        <v>-349.7459727847604</v>
       </c>
       <c r="D81">
-        <v>388.8900889270708</v>
+        <v>385.1940272152397</v>
       </c>
       <c r="E81">
-        <v>379.2670000000002</v>
+        <v>389.7400000000001</v>
       </c>
       <c r="F81">
-        <v>827.3670000000002</v>
+        <v>837.8400000000001</v>
       </c>
       <c r="G81">
         <v>102.9</v>
@@ -7935,37 +7935,37 @@
         <v>109.325</v>
       </c>
       <c r="M81">
-        <v>121.4574756</v>
+        <v>122.994912</v>
       </c>
       <c r="N81">
-        <v>-12.13247560000005</v>
+        <v>-13.66991200000004</v>
       </c>
       <c r="O81">
-        <v>-1.516559450000006</v>
+        <v>-1.708739000000005</v>
       </c>
       <c r="P81">
-        <v>-10.61591615000004</v>
+        <v>-11.96117300000003</v>
       </c>
       <c r="Q81">
-        <v>3.684083849999968</v>
+        <v>2.338826999999977</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2292191971272503</v>
+        <v>0.2383901569836128</v>
       </c>
       <c r="T81">
-        <v>3.575181549982189</v>
+        <v>3.753940627481299</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.112513659060439</v>
+        <v>0.1111072383221836</v>
       </c>
       <c r="W81">
-        <v>0.1302829948499276</v>
+        <v>0.1304894574143035</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9001092724835124</v>
+        <v>0.8888579065774685</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1520695973281653</v>
+        <v>0.1530795973281653</v>
       </c>
       <c r="C82">
-        <v>-349.7459727847604</v>
+        <v>-363.8454402322222</v>
       </c>
       <c r="D82">
-        <v>385.1940272152397</v>
+        <v>381.5675597677779</v>
       </c>
       <c r="E82">
-        <v>389.7400000000001</v>
+        <v>400.2130000000002</v>
       </c>
       <c r="F82">
-        <v>837.8400000000001</v>
+        <v>848.3130000000002</v>
       </c>
       <c r="G82">
         <v>102.9</v>
@@ -8017,37 +8017,37 @@
         <v>109.325</v>
       </c>
       <c r="M82">
-        <v>122.994912</v>
+        <v>124.5323484</v>
       </c>
       <c r="N82">
-        <v>-13.66991200000004</v>
+        <v>-15.20734840000006</v>
       </c>
       <c r="O82">
-        <v>-1.708739000000005</v>
+        <v>-1.900918550000007</v>
       </c>
       <c r="P82">
-        <v>-11.96117300000003</v>
+        <v>-13.30642985000005</v>
       </c>
       <c r="Q82">
-        <v>2.338826999999977</v>
+        <v>0.993570149999961</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2383901569836128</v>
+        <v>0.2485264810353819</v>
       </c>
       <c r="T82">
-        <v>3.753940627481299</v>
+        <v>3.951516449980315</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1111072383221836</v>
+        <v>0.1097355440219097</v>
       </c>
       <c r="W82">
-        <v>0.1304894574143035</v>
+        <v>0.1306908221375837</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8888579065774685</v>
+        <v>0.8778843521752775</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1530795973281653</v>
+        <v>0.1540895973281653</v>
       </c>
       <c r="C83">
-        <v>-363.8454402322222</v>
+        <v>-377.8772606995066</v>
       </c>
       <c r="D83">
-        <v>381.5675597677779</v>
+        <v>378.0087393004936</v>
       </c>
       <c r="E83">
-        <v>400.2130000000002</v>
+        <v>410.6860000000001</v>
       </c>
       <c r="F83">
-        <v>848.3130000000002</v>
+        <v>858.7860000000002</v>
       </c>
       <c r="G83">
         <v>102.9</v>
@@ -8099,37 +8099,37 @@
         <v>109.325</v>
       </c>
       <c r="M83">
-        <v>124.5323484</v>
+        <v>126.0697848</v>
       </c>
       <c r="N83">
-        <v>-15.20734840000006</v>
+        <v>-16.74478480000005</v>
       </c>
       <c r="O83">
-        <v>-1.900918550000007</v>
+        <v>-2.093098100000006</v>
       </c>
       <c r="P83">
-        <v>-13.30642985000005</v>
+        <v>-14.65168670000004</v>
       </c>
       <c r="Q83">
-        <v>0.993570149999961</v>
+        <v>-0.3516867000000303</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2485264810353819</v>
+        <v>0.2597890633151254</v>
       </c>
       <c r="T83">
-        <v>3.951516449980315</v>
+        <v>4.171045141645888</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1097355440219097</v>
+        <v>0.1083973056801791</v>
       </c>
       <c r="W83">
-        <v>0.1306908221375837</v>
+        <v>0.1308872755261497</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8778843521752775</v>
+        <v>0.8671784454414326</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1540895973281653</v>
+        <v>0.1550995973281653</v>
       </c>
       <c r="C84">
-        <v>-377.8772606995066</v>
+        <v>-391.8433094940708</v>
       </c>
       <c r="D84">
-        <v>378.0087393004936</v>
+        <v>374.5156905059294</v>
       </c>
       <c r="E84">
-        <v>410.6860000000001</v>
+        <v>421.1590000000002</v>
       </c>
       <c r="F84">
-        <v>858.7860000000002</v>
+        <v>869.2590000000002</v>
       </c>
       <c r="G84">
         <v>102.9</v>
@@ -8181,37 +8181,37 @@
         <v>109.325</v>
       </c>
       <c r="M84">
-        <v>126.0697848</v>
+        <v>127.6072212</v>
       </c>
       <c r="N84">
-        <v>-16.74478480000005</v>
+        <v>-18.28222120000005</v>
       </c>
       <c r="O84">
-        <v>-2.093098100000006</v>
+        <v>-2.285277650000006</v>
       </c>
       <c r="P84">
-        <v>-14.65168670000004</v>
+        <v>-15.99694355000005</v>
       </c>
       <c r="Q84">
-        <v>-0.3516867000000303</v>
+        <v>-1.696943550000034</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2597890633151254</v>
+        <v>0.2723766552748386</v>
       </c>
       <c r="T84">
-        <v>4.171045141645888</v>
+        <v>4.416400738213293</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1083973056801791</v>
+        <v>0.1070913140454781</v>
       </c>
       <c r="W84">
-        <v>0.1308872755261497</v>
+        <v>0.1310789950981238</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8671784454414326</v>
+        <v>0.856730512363825</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1550995973281653</v>
+        <v>0.1561095973281653</v>
       </c>
       <c r="C85">
-        <v>-391.8433094940708</v>
+        <v>-405.7453932417493</v>
       </c>
       <c r="D85">
-        <v>374.5156905059294</v>
+        <v>371.0866067582509</v>
       </c>
       <c r="E85">
-        <v>421.1590000000002</v>
+        <v>431.6320000000002</v>
       </c>
       <c r="F85">
-        <v>869.2590000000002</v>
+        <v>879.7320000000002</v>
       </c>
       <c r="G85">
         <v>102.9</v>
@@ -8263,37 +8263,37 @@
         <v>109.325</v>
       </c>
       <c r="M85">
-        <v>127.6072212</v>
+        <v>129.1446576</v>
       </c>
       <c r="N85">
-        <v>-18.28222120000005</v>
+        <v>-19.81965760000006</v>
       </c>
       <c r="O85">
-        <v>-2.285277650000006</v>
+        <v>-2.477457200000007</v>
       </c>
       <c r="P85">
-        <v>-15.99694355000005</v>
+        <v>-17.34220040000005</v>
       </c>
       <c r="Q85">
-        <v>-1.696943550000034</v>
+        <v>-3.042200400000038</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2723766552748386</v>
+        <v>0.286537696229516</v>
       </c>
       <c r="T85">
-        <v>4.416400738213293</v>
+        <v>4.692425784351625</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1070913140454781</v>
+        <v>0.1058164174496986</v>
       </c>
       <c r="W85">
-        <v>0.1310789950981238</v>
+        <v>0.1312661499183843</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.856730512363825</v>
+        <v>0.846531339597589</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1561095973281653</v>
+        <v>0.1571195973281653</v>
       </c>
       <c r="C86">
-        <v>-405.7453932417492</v>
+        <v>-419.5852530024881</v>
       </c>
       <c r="D86">
-        <v>371.0866067582509</v>
+        <v>367.7197469975121</v>
       </c>
       <c r="E86">
-        <v>431.6320000000001</v>
+        <v>442.1050000000001</v>
       </c>
       <c r="F86">
-        <v>879.7320000000001</v>
+        <v>890.2050000000002</v>
       </c>
       <c r="G86">
         <v>102.9</v>
@@ -8345,37 +8345,37 @@
         <v>109.325</v>
       </c>
       <c r="M86">
-        <v>129.1446576</v>
+        <v>130.682094</v>
       </c>
       <c r="N86">
-        <v>-19.81965760000003</v>
+        <v>-21.35709400000005</v>
       </c>
       <c r="O86">
-        <v>-2.477457200000003</v>
+        <v>-2.669636750000006</v>
       </c>
       <c r="P86">
-        <v>-17.34220040000002</v>
+        <v>-18.68745725000004</v>
       </c>
       <c r="Q86">
-        <v>-3.042200400000013</v>
+        <v>-4.387457250000029</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2865376962295159</v>
+        <v>0.3025868759781503</v>
       </c>
       <c r="T86">
-        <v>4.692425784351622</v>
+        <v>5.005254169975063</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1058164174496986</v>
+        <v>0.1045715184208787</v>
       </c>
       <c r="W86">
-        <v>0.1312661499183843</v>
+        <v>0.131448901095815</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8465313395975892</v>
+        <v>0.8365721473670291</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1571195973281653</v>
+        <v>0.1581295973281653</v>
       </c>
       <c r="C87">
-        <v>-419.5852530024881</v>
+        <v>-433.3645672179879</v>
       </c>
       <c r="D87">
-        <v>367.7197469975121</v>
+        <v>364.4134327820123</v>
       </c>
       <c r="E87">
-        <v>442.1050000000001</v>
+        <v>452.5780000000001</v>
       </c>
       <c r="F87">
-        <v>890.2050000000002</v>
+        <v>900.6780000000001</v>
       </c>
       <c r="G87">
         <v>102.9</v>
@@ -8427,37 +8427,37 @@
         <v>109.325</v>
       </c>
       <c r="M87">
-        <v>130.682094</v>
+        <v>132.2195304</v>
       </c>
       <c r="N87">
-        <v>-21.35709400000005</v>
+        <v>-22.89453040000004</v>
       </c>
       <c r="O87">
-        <v>-2.669636750000006</v>
+        <v>-2.861816300000005</v>
       </c>
       <c r="P87">
-        <v>-18.68745725000004</v>
+        <v>-20.03271410000003</v>
       </c>
       <c r="Q87">
-        <v>-4.387457250000029</v>
+        <v>-5.73271410000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3025868759781503</v>
+        <v>0.3209287956908753</v>
       </c>
       <c r="T87">
-        <v>5.005254169975063</v>
+        <v>5.362772324973283</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1045715184208787</v>
+        <v>0.1033555705322638</v>
       </c>
       <c r="W87">
-        <v>0.131448901095815</v>
+        <v>0.1316274022458637</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8365721473670291</v>
+        <v>0.8268445642581103</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1581295973281653</v>
+        <v>0.1591395973281653</v>
       </c>
       <c r="C88">
-        <v>-433.3645672179879</v>
+        <v>-447.0849545017468</v>
       </c>
       <c r="D88">
-        <v>364.4134327820123</v>
+        <v>361.1660454982534</v>
       </c>
       <c r="E88">
-        <v>452.5780000000001</v>
+        <v>463.0510000000002</v>
       </c>
       <c r="F88">
-        <v>900.6780000000001</v>
+        <v>911.1510000000002</v>
       </c>
       <c r="G88">
         <v>102.9</v>
@@ -8509,37 +8509,37 @@
         <v>109.325</v>
       </c>
       <c r="M88">
-        <v>132.2195304</v>
+        <v>133.7569668</v>
       </c>
       <c r="N88">
-        <v>-22.89453040000004</v>
+        <v>-24.43196680000005</v>
       </c>
       <c r="O88">
-        <v>-2.861816300000005</v>
+        <v>-3.053995850000007</v>
       </c>
       <c r="P88">
-        <v>-20.03271410000003</v>
+        <v>-21.37797095000005</v>
       </c>
       <c r="Q88">
-        <v>-5.73271410000002</v>
+        <v>-7.077970950000037</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3209287956908753</v>
+        <v>0.342092549205558</v>
       </c>
       <c r="T88">
-        <v>5.362772324973283</v>
+        <v>5.77529327304815</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1033555705322638</v>
+        <v>0.1021675754686745</v>
       </c>
       <c r="W88">
-        <v>0.1316274022458637</v>
+        <v>0.1318017999211986</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8268445642581103</v>
+        <v>0.8173406037493962</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1591395973281653</v>
+        <v>0.1601495973281653</v>
       </c>
       <c r="C89">
-        <v>-447.0849545017468</v>
+        <v>-460.7479762812408</v>
       </c>
       <c r="D89">
-        <v>361.1660454982534</v>
+        <v>357.9760237187593</v>
       </c>
       <c r="E89">
-        <v>463.0510000000002</v>
+        <v>473.5240000000001</v>
       </c>
       <c r="F89">
-        <v>911.1510000000002</v>
+        <v>921.6240000000001</v>
       </c>
       <c r="G89">
         <v>102.9</v>
@@ -8591,37 +8591,37 @@
         <v>109.325</v>
       </c>
       <c r="M89">
-        <v>133.7569668</v>
+        <v>135.2944032</v>
       </c>
       <c r="N89">
-        <v>-24.43196680000005</v>
+        <v>-25.96940320000004</v>
       </c>
       <c r="O89">
-        <v>-3.053995850000007</v>
+        <v>-3.246175400000006</v>
       </c>
       <c r="P89">
-        <v>-21.37797095000005</v>
+        <v>-22.72322780000004</v>
       </c>
       <c r="Q89">
-        <v>-7.077970950000037</v>
+        <v>-8.423227800000028</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.342092549205558</v>
+        <v>0.3667835949726879</v>
       </c>
       <c r="T89">
-        <v>5.77529327304815</v>
+        <v>6.25656771246883</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1021675754686745</v>
+        <v>0.1010065802928942</v>
       </c>
       <c r="W89">
-        <v>0.1318017999211986</v>
+        <v>0.1319722340130031</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8173406037493962</v>
+        <v>0.8080526423431532</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1601495973281653</v>
+        <v>0.2102301376668381</v>
       </c>
       <c r="C90">
-        <v>-460.7479762812408</v>
+        <v>-580.2498498837751</v>
       </c>
       <c r="D90">
-        <v>357.9760237187593</v>
+        <v>248.947150116225</v>
       </c>
       <c r="E90">
-        <v>473.5240000000001</v>
+        <v>483.9970000000002</v>
       </c>
       <c r="F90">
-        <v>921.6240000000001</v>
+        <v>932.0970000000002</v>
       </c>
       <c r="G90">
         <v>102.9</v>
@@ -8673,45 +8673,45 @@
         <v>109.325</v>
       </c>
       <c r="M90">
-        <v>135.2944032</v>
+        <v>187.1650776</v>
       </c>
       <c r="N90">
-        <v>-25.96940320000004</v>
+        <v>-77.84007760000006</v>
       </c>
       <c r="O90">
-        <v>-3.246175400000006</v>
+        <v>-9.730009700000007</v>
       </c>
       <c r="P90">
-        <v>-22.72322780000004</v>
+        <v>-68.11006790000005</v>
       </c>
       <c r="Q90">
-        <v>-8.423227800000028</v>
+        <v>-53.81006790000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3667835949726879</v>
+        <v>0.4051506521399569</v>
       </c>
       <c r="T90">
-        <v>6.25656771246883</v>
+        <v>7.004413069224855</v>
       </c>
       <c r="U90">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1010065802928942</v>
+        <v>0.0730137543564911</v>
       </c>
       <c r="W90">
-        <v>0.1319722340130031</v>
+        <v>0.1861388381252166</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8080526423431532</v>
+        <v>0.5841100348519288</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2102301376668381</v>
+        <v>0.211780137666838</v>
       </c>
       <c r="C91">
-        <v>-580.2498498837751</v>
+        <v>-593.047634572499</v>
       </c>
       <c r="D91">
-        <v>248.947150116225</v>
+        <v>246.6223654275012</v>
       </c>
       <c r="E91">
-        <v>483.9970000000002</v>
+        <v>494.4700000000001</v>
       </c>
       <c r="F91">
-        <v>932.0970000000002</v>
+        <v>942.5700000000002</v>
       </c>
       <c r="G91">
         <v>102.9</v>
@@ -8755,37 +8755,37 @@
         <v>109.325</v>
       </c>
       <c r="M91">
-        <v>187.1650776</v>
+        <v>189.268056</v>
       </c>
       <c r="N91">
-        <v>-77.84007760000006</v>
+        <v>-79.94305600000004</v>
       </c>
       <c r="O91">
-        <v>-9.730009700000007</v>
+        <v>-9.992882000000005</v>
       </c>
       <c r="P91">
-        <v>-68.11006790000005</v>
+        <v>-69.95017400000003</v>
       </c>
       <c r="Q91">
-        <v>-53.81006790000004</v>
+        <v>-55.65017400000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4051506521399569</v>
+        <v>0.4410857173539527</v>
       </c>
       <c r="T91">
-        <v>7.004413069224855</v>
+        <v>7.704854376147341</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.0730137543564911</v>
+        <v>0.07220249041919677</v>
       </c>
       <c r="W91">
-        <v>0.1861388381252166</v>
+        <v>0.1863017399238253</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5841100348519288</v>
+        <v>0.5776199233535741</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.211780137666838</v>
+        <v>0.213330137666838</v>
       </c>
       <c r="C92">
-        <v>-593.047634572499</v>
+        <v>-605.8024011354372</v>
       </c>
       <c r="D92">
-        <v>246.6223654275012</v>
+        <v>244.340598864563</v>
       </c>
       <c r="E92">
-        <v>494.4700000000001</v>
+        <v>504.9430000000002</v>
       </c>
       <c r="F92">
-        <v>942.5700000000002</v>
+        <v>953.0430000000002</v>
       </c>
       <c r="G92">
         <v>102.9</v>
@@ -8837,37 +8837,37 @@
         <v>109.325</v>
       </c>
       <c r="M92">
-        <v>189.268056</v>
+        <v>191.3710344</v>
       </c>
       <c r="N92">
-        <v>-79.94305600000004</v>
+        <v>-82.04603440000005</v>
       </c>
       <c r="O92">
-        <v>-9.992882000000005</v>
+        <v>-10.25575430000001</v>
       </c>
       <c r="P92">
-        <v>-69.95017400000003</v>
+        <v>-71.79028010000005</v>
       </c>
       <c r="Q92">
-        <v>-55.65017400000002</v>
+        <v>-57.49028010000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4410857173539527</v>
+        <v>0.4850063526155031</v>
       </c>
       <c r="T92">
-        <v>7.704854376147341</v>
+        <v>8.560949306830381</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07220249041919677</v>
+        <v>0.07140905645854624</v>
       </c>
       <c r="W92">
-        <v>0.1863017399238253</v>
+        <v>0.1864610614631239</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5776199233535741</v>
+        <v>0.57127245166837</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.213330137666838</v>
+        <v>0.214880137666838</v>
       </c>
       <c r="C93">
-        <v>-605.8024011354372</v>
+        <v>-618.5153326464131</v>
       </c>
       <c r="D93">
-        <v>244.340598864563</v>
+        <v>242.1006673535872</v>
       </c>
       <c r="E93">
-        <v>504.9430000000002</v>
+        <v>515.4160000000002</v>
       </c>
       <c r="F93">
-        <v>953.0430000000002</v>
+        <v>963.5160000000002</v>
       </c>
       <c r="G93">
         <v>102.9</v>
@@ -8919,37 +8919,37 @@
         <v>109.325</v>
       </c>
       <c r="M93">
-        <v>191.3710344</v>
+        <v>193.4740128000001</v>
       </c>
       <c r="N93">
-        <v>-82.04603440000005</v>
+        <v>-84.14901280000007</v>
       </c>
       <c r="O93">
-        <v>-10.25575430000001</v>
+        <v>-10.51862660000001</v>
       </c>
       <c r="P93">
-        <v>-71.79028010000005</v>
+        <v>-73.63038620000006</v>
       </c>
       <c r="Q93">
-        <v>-57.49028010000004</v>
+        <v>-59.33038620000005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4850063526155031</v>
+        <v>0.5399071466924409</v>
       </c>
       <c r="T93">
-        <v>8.560949306830381</v>
+        <v>9.631067970184178</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07140905645854624</v>
+        <v>0.0706328710622577</v>
       </c>
       <c r="W93">
-        <v>0.1864610614631239</v>
+        <v>0.1866169194906987</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.57127245166837</v>
+        <v>0.5650629684980615</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.214880137666838</v>
+        <v>0.216430137666838</v>
       </c>
       <c r="C94">
-        <v>-618.5153326464131</v>
+        <v>-631.1875691911948</v>
       </c>
       <c r="D94">
-        <v>242.1006673535872</v>
+        <v>239.9014308088054</v>
       </c>
       <c r="E94">
-        <v>515.4160000000002</v>
+        <v>525.8890000000002</v>
       </c>
       <c r="F94">
-        <v>963.5160000000002</v>
+        <v>973.9890000000003</v>
       </c>
       <c r="G94">
         <v>102.9</v>
@@ -9001,37 +9001,37 @@
         <v>109.325</v>
       </c>
       <c r="M94">
-        <v>193.4740128000001</v>
+        <v>195.5769912000001</v>
       </c>
       <c r="N94">
-        <v>-84.14901280000007</v>
+        <v>-86.25199120000008</v>
       </c>
       <c r="O94">
-        <v>-10.51862660000001</v>
+        <v>-10.78149890000001</v>
       </c>
       <c r="P94">
-        <v>-73.63038620000006</v>
+        <v>-75.47049230000007</v>
       </c>
       <c r="Q94">
-        <v>-59.33038620000005</v>
+        <v>-61.17049230000006</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5399071466924409</v>
+        <v>0.6104938819342183</v>
       </c>
       <c r="T94">
-        <v>9.631067970184178</v>
+        <v>11.00693482306763</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.0706328710622577</v>
+        <v>0.06987337782502911</v>
       </c>
       <c r="W94">
-        <v>0.1866169194906987</v>
+        <v>0.1867694257327342</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5650629684980615</v>
+        <v>0.5589870226002329</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.216430137666838</v>
+        <v>0.217980137666838</v>
       </c>
       <c r="C95">
-        <v>-631.1875691911948</v>
+        <v>-643.8202098024316</v>
       </c>
       <c r="D95">
-        <v>239.9014308088054</v>
+        <v>237.7417901975686</v>
       </c>
       <c r="E95">
-        <v>525.8890000000002</v>
+        <v>536.3620000000002</v>
       </c>
       <c r="F95">
-        <v>973.9890000000003</v>
+        <v>984.4620000000002</v>
       </c>
       <c r="G95">
         <v>102.9</v>
@@ -9083,37 +9083,37 @@
         <v>109.325</v>
       </c>
       <c r="M95">
-        <v>195.5769912000001</v>
+        <v>197.6799696</v>
       </c>
       <c r="N95">
-        <v>-86.25199120000008</v>
+        <v>-88.35496960000006</v>
       </c>
       <c r="O95">
-        <v>-10.78149890000001</v>
+        <v>-11.04437120000001</v>
       </c>
       <c r="P95">
-        <v>-75.47049230000007</v>
+        <v>-77.31059840000006</v>
       </c>
       <c r="Q95">
-        <v>-61.17049230000006</v>
+        <v>-63.01059840000005</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6104938819342183</v>
+        <v>0.7046095289232548</v>
       </c>
       <c r="T95">
-        <v>11.00693482306763</v>
+        <v>12.84142396024558</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06987337782502911</v>
+        <v>0.06913004401837987</v>
       </c>
       <c r="W95">
-        <v>0.1867694257327342</v>
+        <v>0.1869186871611093</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5589870226002329</v>
+        <v>0.5530403521470391</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.217980137666838</v>
+        <v>0.219530137666838</v>
       </c>
       <c r="C96">
-        <v>-643.8202098024316</v>
+        <v>-656.4143142910087</v>
       </c>
       <c r="D96">
-        <v>237.7417901975686</v>
+        <v>235.6206857089915</v>
       </c>
       <c r="E96">
-        <v>536.3620000000002</v>
+        <v>546.8350000000003</v>
       </c>
       <c r="F96">
-        <v>984.4620000000002</v>
+        <v>994.9350000000003</v>
       </c>
       <c r="G96">
         <v>102.9</v>
@@ -9165,37 +9165,37 @@
         <v>109.325</v>
       </c>
       <c r="M96">
-        <v>197.6799696</v>
+        <v>199.7829480000001</v>
       </c>
       <c r="N96">
-        <v>-88.35496960000006</v>
+        <v>-90.45794800000007</v>
       </c>
       <c r="O96">
-        <v>-11.04437120000001</v>
+        <v>-11.30724350000001</v>
       </c>
       <c r="P96">
-        <v>-77.31059840000006</v>
+        <v>-79.15070450000006</v>
       </c>
       <c r="Q96">
-        <v>-63.01059840000005</v>
+        <v>-64.85070450000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7046095289232548</v>
+        <v>0.8363714347079061</v>
       </c>
       <c r="T96">
-        <v>12.84142396024558</v>
+        <v>15.4097087522947</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06913004401837987</v>
+        <v>0.06840235934450219</v>
       </c>
       <c r="W96">
-        <v>0.1869186871611093</v>
+        <v>0.187064806243624</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5530403521470391</v>
+        <v>0.5472188747560175</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.219530137666838</v>
+        <v>0.221080137666838</v>
       </c>
       <c r="C97">
-        <v>-656.4143142910087</v>
+        <v>-668.970904980235</v>
       </c>
       <c r="D97">
-        <v>235.6206857089915</v>
+        <v>233.5370950197652</v>
       </c>
       <c r="E97">
-        <v>546.8350000000003</v>
+        <v>557.3080000000002</v>
       </c>
       <c r="F97">
-        <v>994.9350000000003</v>
+        <v>1005.408</v>
       </c>
       <c r="G97">
         <v>102.9</v>
@@ -9247,37 +9247,37 @@
         <v>109.325</v>
       </c>
       <c r="M97">
-        <v>199.7829480000001</v>
+        <v>201.8859264</v>
       </c>
       <c r="N97">
-        <v>-90.45794800000007</v>
+        <v>-92.56092640000006</v>
       </c>
       <c r="O97">
-        <v>-11.30724350000001</v>
+        <v>-11.57011580000001</v>
       </c>
       <c r="P97">
-        <v>-79.15070450000006</v>
+        <v>-80.99081060000005</v>
       </c>
       <c r="Q97">
-        <v>-64.85070450000005</v>
+        <v>-66.69081060000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8363714347079061</v>
+        <v>1.034014293384883</v>
       </c>
       <c r="T97">
-        <v>15.4097087522947</v>
+        <v>19.26213594036838</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06840235934450219</v>
+        <v>0.06768983476799696</v>
       </c>
       <c r="W97">
-        <v>0.187064806243624</v>
+        <v>0.1872078811785862</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5472188747560175</v>
+        <v>0.5415186781439757</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.221080137666838</v>
+        <v>0.222630137666838</v>
       </c>
       <c r="C98">
-        <v>-668.970904980235</v>
+        <v>-681.4909683488257</v>
       </c>
       <c r="D98">
-        <v>233.5370950197652</v>
+        <v>231.4900316511745</v>
       </c>
       <c r="E98">
-        <v>557.3080000000001</v>
+        <v>567.7810000000002</v>
       </c>
       <c r="F98">
-        <v>1005.408</v>
+        <v>1015.881</v>
       </c>
       <c r="G98">
         <v>102.9</v>
@@ -9329,37 +9329,37 @@
         <v>109.325</v>
       </c>
       <c r="M98">
-        <v>201.8859264</v>
+        <v>203.9889048000001</v>
       </c>
       <c r="N98">
-        <v>-92.56092640000006</v>
+        <v>-94.66390480000007</v>
       </c>
       <c r="O98">
-        <v>-11.57011580000001</v>
+        <v>-11.83298810000001</v>
       </c>
       <c r="P98">
-        <v>-80.99081060000005</v>
+        <v>-82.83091670000006</v>
       </c>
       <c r="Q98">
-        <v>-66.69081060000003</v>
+        <v>-68.53091670000005</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.034014293384881</v>
+        <v>1.363419057846508</v>
       </c>
       <c r="T98">
-        <v>19.26213594036833</v>
+        <v>25.68284792049111</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06768983476799696</v>
+        <v>0.06699200141987327</v>
       </c>
       <c r="W98">
-        <v>0.1872078811785862</v>
+        <v>0.1873480061148894</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5415186781439757</v>
+        <v>0.5359360113589862</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.222630137666838</v>
+        <v>0.224180137666838</v>
       </c>
       <c r="C99">
-        <v>-681.4909683488257</v>
+        <v>-693.9754565882254</v>
       </c>
       <c r="D99">
-        <v>231.4900316511745</v>
+        <v>229.4785434117749</v>
       </c>
       <c r="E99">
-        <v>567.7810000000002</v>
+        <v>578.2540000000002</v>
       </c>
       <c r="F99">
-        <v>1015.881</v>
+        <v>1026.354</v>
       </c>
       <c r="G99">
         <v>102.9</v>
@@ -9411,37 +9411,37 @@
         <v>109.325</v>
       </c>
       <c r="M99">
-        <v>203.9889048000001</v>
+        <v>206.0918832000001</v>
       </c>
       <c r="N99">
-        <v>-94.66390480000007</v>
+        <v>-96.76688320000008</v>
       </c>
       <c r="O99">
-        <v>-11.83298810000001</v>
+        <v>-12.09586040000001</v>
       </c>
       <c r="P99">
-        <v>-82.83091670000006</v>
+        <v>-84.67102280000007</v>
       </c>
       <c r="Q99">
-        <v>-68.53091670000005</v>
+        <v>-70.37102280000006</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.363419057846508</v>
+        <v>2.022228586769761</v>
       </c>
       <c r="T99">
-        <v>25.68284792049111</v>
+        <v>38.52427188073666</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06699200141987327</v>
+        <v>0.06630840956865007</v>
       </c>
       <c r="W99">
-        <v>0.1873480061148894</v>
+        <v>0.1874852713586151</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5359360113589862</v>
+        <v>0.5304672765492007</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.224180137666838</v>
+        <v>0.225730137666838</v>
       </c>
       <c r="C100">
-        <v>-693.9754565882254</v>
+        <v>-706.4252890794384</v>
       </c>
       <c r="D100">
-        <v>229.4785434117749</v>
+        <v>227.5017109205619</v>
       </c>
       <c r="E100">
-        <v>578.2540000000002</v>
+        <v>588.7270000000002</v>
       </c>
       <c r="F100">
-        <v>1026.354</v>
+        <v>1036.827</v>
       </c>
       <c r="G100">
         <v>102.9</v>
@@ -9493,37 +9493,37 @@
         <v>109.325</v>
       </c>
       <c r="M100">
-        <v>206.0918832000001</v>
+        <v>208.1948616000001</v>
       </c>
       <c r="N100">
-        <v>-96.76688320000008</v>
+        <v>-98.86986160000006</v>
       </c>
       <c r="O100">
-        <v>-12.09586040000001</v>
+        <v>-12.35873270000001</v>
       </c>
       <c r="P100">
-        <v>-84.67102280000007</v>
+        <v>-86.51112890000006</v>
       </c>
       <c r="Q100">
-        <v>-70.37102280000006</v>
+        <v>-72.21112890000005</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.022228586769761</v>
+        <v>3.998657173539522</v>
       </c>
       <c r="T100">
-        <v>38.52427188073666</v>
+        <v>77.04854376147333</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06630840956865007</v>
+        <v>0.06563862765381523</v>
       </c>
       <c r="W100">
-        <v>0.1874852713586151</v>
+        <v>0.1876197635671139</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5304672765492007</v>
+        <v>0.5251090212305218</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.225730137666838</v>
-      </c>
-      <c r="C101">
-        <v>-706.4252890794384</v>
-      </c>
-      <c r="D101">
-        <v>227.5017109205619</v>
-      </c>
-      <c r="E101">
-        <v>588.7270000000002</v>
-      </c>
-      <c r="F101">
-        <v>1036.827</v>
-      </c>
-      <c r="G101">
-        <v>102.9</v>
-      </c>
-      <c r="H101">
-        <v>599.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>123.625</v>
-      </c>
-      <c r="K101">
-        <v>14.30000000000001</v>
-      </c>
-      <c r="L101">
-        <v>109.325</v>
-      </c>
-      <c r="M101">
-        <v>208.1948616000001</v>
-      </c>
-      <c r="N101">
-        <v>-98.86986160000006</v>
-      </c>
-      <c r="O101">
-        <v>-12.35873270000001</v>
-      </c>
-      <c r="P101">
-        <v>-86.51112890000006</v>
-      </c>
-      <c r="Q101">
-        <v>-72.21112890000005</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.998657173539522</v>
-      </c>
-      <c r="T101">
-        <v>77.04854376147333</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.06563862765381523</v>
-      </c>
-      <c r="W101">
-        <v>0.1876197635671139</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5251090212305218</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
